--- a/untitled folder/HSC_Physics_1st_Paper_Chapter_02_Vector.xlsx
+++ b/untitled folder/HSC_Physics_1st_Paper_Chapter_02_Vector.xlsx
@@ -1223,11 +1223,6 @@
           <t>একটি বিন্দু থেকে একই সমতলে $n$-সংখ্যক সমান মানের ($F$) বল ক্রিয়ারত, যাদের পরপর দুটি বলের মধ্যবর্তী কোণ $\frac{2\pi}{n}$। বলগুলোর ভেক্টর যোগফল কেন শূন্য হবে? যদি এদের মধ্য থেকে যেকোনো একটি বল সরিয়ে নেওয়া হয়, তবে অবশিষ্ট $(n-1)$ টি বলের লব্ধির মান ও দিক কী হবে?</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I3" t="inlineStr">
         <is>
           <t>১. প্রতিসাম্য অনুসারে $n$-সংখ্যক সমান বল একটি সুষম $n$-ভুজ (Regular polygon) গঠন করে। বহুভুজ সূত্রানুযায়ী একটি বদ্ধ বহুভুজের ক্রমানুসারে গৃহীত বাহুগুলোর ভেক্টর যোগফল শূন্য:
@@ -1275,11 +1270,6 @@
       <c r="G4" t="inlineStr">
         <is>
           <t>একটি বিন্দুতে তিনটি বল $\vec{P}, \vec{Q}, \vec{R}$ সাম্যাবস্থায় রয়েছে। $\vec{P}$ ও $\vec{Q}$-এর মধ্যবর্তী কোণ $150^\circ$ এবং $\vec{Q}$ ও $\vec{R}$-এর মধ্যবর্তী কোণ $120^\circ$। বল তিনটির মানের অনুপাত $P : Q : R$ নির্ণয় করো। লামির উপপাদ্য প্রয়োগের জন্য বলগুলোর সমবিন্দুগামী ও একসমতলীয় হওয়া কেন বাধ্যতামূলক?</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1294,7 +1284,7 @@
 $\frac{P}{\sqrt{3}/2} = \frac{Q}{1} = \frac{R}{1/2}$।
 ৩. উভয় পক্ষকে ২ দিয়ে গুণ করে পাই:
 $\frac{P}{\sqrt{3}} = \frac{Q}{1} = \frac{R}{2} \implies P : Q : R = \sqrt{3} : 1 : 2$।
-৪. লামির উপপাদ্যটি ত্রিভুজের সাইন সূত্র ($rac{a}{\sin A} = rac{b}{\sin B} = rac{c}{\sin C}$) থেকে উদ্ভূত, যা কেবল একটি দ্বিমাত্রিক সমতলে গঠিত বদ্ধ ত্রিভুজের জন্যই বৈধ।</t>
+৪. লামির উপপাদ্যটি ত্রিভুজের সাইন সূত্র ($\frac{a}{\sin A} = \frac{b}{\sin B} = \frac{c}{\sin C}$) থেকে উদ্ভূত, যা কেবল একটি দ্বিমাত্রিক সমতলে গঠিত বদ্ধ ত্রিভুজের জন্যই বৈধ।</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1335,11 +1325,6 @@
       <c r="G5" t="inlineStr">
         <is>
           <t>দুটি ভেক্টর $\vec{A}$ ও $\vec{B}$-এর জন্য প্রমাণ করো যে $||A| - |B|| \le |\vec{A} + \vec{B}| \le |A| + |B|$। এই অসমতার জ্যামিতিক তাৎপর্য কী এবং কোন শর্তে সমতাচিহ্ন প্রযোজ্য হয়?</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1389,11 +1374,6 @@
       <c r="G6" t="inlineStr">
         <is>
           <t>একটি ভেক্টর $\vec{V}$ তিনটি অক্ষ $x, y, z$-এর ধনাত্মক দিকের সাথে যথাক্রমে $\alpha, \beta, \gamma$ কোণ উৎপন্ন করে। প্রমাণ করো যে $\cos^2 \alpha + \cos^2 \beta + \cos^2 \gamma = 1$ এবং $\sin^2 \alpha + \sin^2 \beta + \sin^2 \gamma = 2$। কোনো ভেক্টর কি তিনটি অক্ষের সাথেই $45^\circ$ কোণ তৈরি করতে পারে?</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1446,11 +1426,6 @@
           <t>একটি ত্রিভুজ $ABC$-এর শীর্ষবিন্দুগুলোর অবস্থান ভেক্টর যথাক্রমে $\vec{a}, \vec{b}, \vec{c}$। ভেক্টর বীজগণিত ব্যবহার করে দেখাও যে ত্রিভুজের মধ্যমাত্রয় পরস্পরকে $2:1$ অনুপাতে যে বিন্দুতে ছেদ করে তার অবস্থান ভেক্টর $\vec{r}_G = \frac{\vec{a} + \vec{b} + \vec{c}}{3}$।</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I7" t="inlineStr">
         <is>
           <t>১. $BC$ বাহুর মধ্যবিন্দু $D$-এর অবস্থান ভেক্টর: $\vec{d} = \frac{\vec{b} + \vec{c}}{2}$।
@@ -1498,11 +1473,6 @@
       <c r="G8" t="inlineStr">
         <is>
           <t>দুটি কণার অবস্থান ভেক্টর যথাক্রমে $\vec{r}_1(t)$ এবং $\vec{r}_2(t)$। ১নং কণার সাপেক্ষে ২নং কণার আপেক্ষিক অবস্থান ভেক্টর $\vec{r}_{21} = \vec{r}_2 - \vec{r}_1$। যদি $|ec{r}_1 + \vec{r}_2| = |\vec{r}_1 - \vec{r}_2|$ হয়, তবে অবস্থান ভেক্টরদ্বয়ের মধ্যবর্তী কোণ কত এবং তাদের জ্যামিতিক অবস্থান কী নির্দেশ করে?</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1553,11 +1523,6 @@
       <c r="G9" t="inlineStr">
         <is>
           <t>তিনটি ভেক্টর $\vec{A} = 2\hat{i} - \hat{j} + \hat{k}$, $\vec{B} = \hat{i} + 2\hat{j} - 3\hat{k}$ এবং $\vec{C} = 3\hat{i} + p\hat{j} + 5\hat{k}$ একই সমতলে অবস্থিত (Coplanar) হলে $p$-এর মান কত? ভেক্টরদের রৈখিক সমাবেশ (Linear combination) $c_1 \vec{A} + c_2 \vec{B} + c_3 \vec{C} = 0$-এর সাথে এর সম্পর্ক কী?</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1665,11 +1630,6 @@
       <c r="G11" t="inlineStr">
         <is>
           <t>যদি একটি দ্বিমাত্রিক কার্তেসীয় অক্ষব্যবস্থাকে মূলবিন্দুর সাপেক্ষে $\theta$ কোণে আবর্তিত করা হয়, তবে একটি ভেক্টরের উপাংশগুলো পরিবর্তিত হয়ে $(V_x', V_y')$ হয়। ম্যাট্রিক্স রূপান্তরের সাহায্যে দেখাও যে অক্ষ আবর্তিত হলেও ভেক্টরের দৈর্ঘ্য $V_x^2 + V_y^2 = (V_x')^2 + (V_y')^2$ অপরিবর্তিত থাকে (Rotational Invariance)।</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1726,11 +1686,6 @@
           <t>একটি ভেক্টর $\vec{A}$ কে অন্য একটি ভেক্টর $\vec{B}$-এর সমান্তরাল এবং লম্ব দুটি উপাংশে বিভক্ত করা হলো: $\vec{A} = \vec{A}_\parallel + \vec{A}_\perp$। ভেক্টর বীজগণিত ব্যবহার করে প্রমাণ করো যে সমান্তরাল উপাংশ $\vec{A}_\parallel = \frac{(\vec{A} \cdot \vec{B})}{B^2} \vec{B}$ এবং লম্ব উপাংশ $\vec{A}_\perp = \frac{\vec{B} \times (\vec{A} \times \vec{B})}{B^2}$।</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I12" t="inlineStr">
         <is>
           <t>১. $\vec{B}$-এর দিকে একক ভেক্টর $\hat{b} = \frac{\vec{B}}{B}$।
@@ -1781,11 +1736,6 @@
           <t>যেকোনো দুটি ভেক্টর $\vec{A}$ ও $\vec{B}$-এর জন্য কশি-সোয়ার্জ অসমতা (Cauchy-Schwarz Inequality) হলো $(\vec{A} \cdot \vec{B})^2 \le |\vec{A}|^2 |\vec{B}|^2$। ডট গুণনের সংজ্ঞা থেকে এটি প্রতিপাদন করো এবং উপাংশ আকারে এটি বীজগাণিতিক $(A_x B_x + A_y B_y + A_z B_z)^2 \le (A_x^2 + A_y^2 + A_z^2)(B_x^2 + B_y^2 + B_z^2)$ রূপ ধারণ করে কেন ব্যাখ্যা করো।</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I13" t="inlineStr">
         <is>
           <t>১. ডট গুণনের সংজ্ঞা: $\vec{A} \cdot \vec{B} = A B \cos \theta$।
@@ -1833,11 +1783,6 @@
       <c r="G14" t="inlineStr">
         <is>
           <t>$a$ বাহুবিশিষ্ট একটি ঘনকের মূলবিন্দুগামী প্রধান কর্ণদ্বয়ের মধ্যবর্তী সূক্ষ্মকোণ ভেক্টর ডট গুণন ব্যবহার করে নির্ণয় করো। $n$-মাত্রিক হাইপারকিউবের প্রধান কর্ণদ্বয়ের মধ্যবর্তী কোণের সাধারণ সূত্রটি কী হবে?</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1890,11 +1835,6 @@
       <c r="G15" t="inlineStr">
         <is>
           <t>একটি কণার ওপর প্রযুক্ত বল $\vec{F} = (2x y)\hat{i} + (x^2 + z)\hat{j} + y\hat{k}$। কণাটিকে মূলবিন্দু $(0,0,0)$ থেকে $(1,2,3)$ বিন্দুতে স্থানান্তরিত করতে কৃতকাজ $W = \int \vec{F} \cdot d\vec{r}$ নির্ণয় করো। বলটি কি সংরক্ষণশীল? পথ-নিরপেক্ষতার প্রমাণ দাও।</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1950,11 +1890,6 @@
           <t>$m_1$ ও $m_2$ ভরের দুটি কণার বেগ যথাক্রমে $\vec{v}_1$ ও $\vec{v}_2$। ডট গুণনের সাহায্যে প্রমাণ করো যে মোট গতিশক্তি $E_k = \frac{1}{2} m_1 v_1^2 + \frac{1}{2} m_2 v_2^2 = \frac{1}{2} M v_{\text{cm}}^2 + \frac{1}{2} \mu v_{\text{rel}}^2$, যেখানে $M = m_1 + m_2$, $\mu = \frac{m_1 m_2}{m_1 + m_2}$ এবং $\vec{v}_{\text{rel}} = \vec{v}_1 - \vec{v}_2$ (কোয়েনিগ উপপাদ্য)।</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I16" t="inlineStr">
         <is>
           <t>১. ভরকেন্দ্রের বেগ: $\vec{v}_{\text{cm}} = \frac{m_1 \vec{v}_1 + m_2 \vec{v}_2}{M}$।
@@ -2008,11 +1943,6 @@
           <t>একটি কণার ওপর প্রযুক্ত বল $\vec{F} = (3t\hat{i} - 2\hat{j} + 4t^2\hat{k})\text{ N}$ এবং কণাটির বেগ $\vec{v} = (2t^2\hat{i} + 3t\hat{j} - \hat{k})\text{ m/s}$। $t = 2\text{ s}$ সময়ে কণাটির ওপর প্রযুক্ত তাত্ক্ষণিক ক্ষমতা $P = \vec{F} \cdot \vec{v}$ কত ওয়াট?</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I17" t="inlineStr">
         <is>
           <t>১. তাত্ক্ষণিক ক্ষমতা: $P(t) = \vec{F} \cdot \vec{v} = (3t)(2t^2) + (-2)(3t) + (4t^2)(-1) = 6t^3 - 6t - 4t^2$।
@@ -2059,11 +1989,6 @@
       <c r="G18" t="inlineStr">
         <is>
           <t>একটি সুষম চৌম্বক ক্ষেত্র $\vec{B}$-তে $q$ আধানবিশিষ্ট কণা $\vec{v}$ বেগে গতিশীল হলে তার ওপর লরেন্টজ চৌম্বক বল $\vec{F}_m = q(\vec{v} \times \vec{B})$। ডট গুণনের সাহায্যে প্রমাণ করো যে স্থির চৌম্বক বল কণার ওপর কোনো কাজ করতে পারে না এবং এর গতিশক্তি সর্বদা ধ্রুব থাকে।</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2113,11 +2038,6 @@
       <c r="G19" t="inlineStr">
         <is>
           <t>একটি দ্বিমাত্রিক তলে একটি কণার গতি $\vec{r}(t) = A \cos(\omega t)\hat{i} + B \sin(\omega t)\hat{j}$। ডট গুণনের সাহায্যে অবস্থান ভেক্টর $\vec{r}$ এবং বেগ ভেক্টর $\vec{v}$ কখন পরস্পর লম্ব হবে তা নির্ণয় করো। কোন বিশেষ শর্তে কণাটির অবস্থান ও ত্বরণ সর্বদা বিপরীতমুখী সমরেখ হয়?</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2173,11 +2093,6 @@
           <t>দুটি ভেক্টর $\vec{u}_1 = 3\hat{i} + 4\hat{j}$ এবং $\vec{u}_2 = \hat{i} + 2\hat{j}$ দেওয়া আছে। গ্রাহাম-শ্মিট লম্বকরণ প্রক্রিয়া (Gram-Schmidt Orthogonalization) প্রয়োগ করে $\vec{u}_1$-এর সমান্তরাল একটি একক ভেক্টর $\hat{e}_1$ এবং $\hat{e}_1$-এর ওপর লম্ব কিন্তু একই সমতলে অবস্থিত দ্বিতীয় একক ভেক্টর $\hat{e}_2$ নির্ণয় করো।</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I20" t="inlineStr">
         <is>
           <t>১. প্রথম একক ভেক্টর: $\hat{e}_1 = \frac{\vec{u}_1}{|\vec{u}_1|} = \frac{3\hat{i} + 4\hat{j}}{\sqrt{3^2 + 4^2}} = \frac{3}{5}\hat{i} + \frac{4}{5}\hat{j}$।
@@ -2230,11 +2145,6 @@
           <t>একটি সমতল দর্পণে আপতিত আলোক রশ্মির দিকে একক ভেক্টর $\hat{u}_i$ এবং আপতন বিন্দুতে বহির্মুখী অভিলম্ব একক ভেক্টর $\hat{n}$। ডট গুণনের সাহায্যে প্রতিফলিত রশ্মির একক ভেক্টর $\hat{u}_r$-এর ভেক্টর সমীকরণ প্রতিপাদন করো এবং দেখাও যে কেন $\hat{u}_r = \hat{u}_i - 2(\hat{u}_i \cdot \hat{n})\hat{n}$।</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I21" t="inlineStr">
         <is>
           <t>১. আপতিত রশ্মি $\hat{u}_i$ কে দর্পণ তলের সমান্তরাল উপাংশ $\hat{u}_{i\parallel}$ এবং লম্ব উপাংশ $\hat{u}_{i\perp}$-এ ভাগ করি:
@@ -2287,11 +2197,6 @@
           <t>একটি সামান্তরিকের দুটি সন্নিহিত বাহু $\vec{A} = 2\hat{i} + 3\hat{j} - \hat{k}$ এবং $\vec{B} = -\hat{i} + \hat{j} + 2\hat{k}$। ক্রস গুণন ব্যবহার করে সামান্তরিকটির ক্ষেত্রফল এবং তার সমতলের ওপর লম্ব একটি একক ভেক্টর নির্ণয় করো।</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I22" t="inlineStr">
         <is>
           <t>১. ক্রস গুণন:
@@ -2339,11 +2244,6 @@
       <c r="G23" t="inlineStr">
         <is>
           <t>যদি একটি সামান্তরিকের দুটি কর্ণ ভেক্টর $\vec{d}_1$ এবং $\vec{d}_2$ হয়, তবে প্রমাণ করো যে সামান্তরিকটির ক্ষেত্রফল হবে $\frac{1}{2}|\vec{d}_1 \times \vec{d}_2|$। সন্নিহিত বাহুর ক্ষেত্রফলের সাথে এর গাণিতিক সম্পর্ক ব্যাখ্যা করো।</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2399,11 +2299,6 @@
           <t>তিনটি সহ-প্রারম্ভিক বাহু $\vec{a} = 2\hat{i} - 3\hat{j} + 4\hat{k}$, $\vec{b} = \hat{i} + 2\hat{j} - \hat{k}$, এবং $\vec{c} = 3\hat{i} - \hat{j} + 2\hat{k}$ দ্বারা গঠিত একটি সামান্তরিক সমবর্তকের (Parallelepiped) আয়তন স্কেলার ট্রিপল প্রোডাক্ট দ্বারা নির্ণয় করো। যদি তিনটি ভেক্টর একসমতলীয় হতো তবে আয়তন কত হতো?</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I24" t="inlineStr">
         <is>
           <t>১. সামান্তরিক সমবর্তকের আয়তন: $V = |\vec{a} \cdot (\vec{b} \times \vec{c})| = |[\vec{a} \ \vec{b} \ \vec{c}]|$
@@ -2455,11 +2350,6 @@
           <t>একটি চতুস্তলকের চারটি শীর্ষবিন্দুর মধ্যে মূলবিন্দুর সাপেক্ষে তিনটি শীর্ষবিন্দুর অবস্থান ভেক্টর $\vec{A}, \vec{B}, \vec{C}$। প্রমাণ করো যে চতুস্তলকটির আয়তন হবে $V = \frac{1}{6}|\vec{A} \cdot (\vec{B} \times \vec{C})|$।</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I25" t="inlineStr">
         <is>
           <t>১. যেকোনো পিরামিড বা চতুস্তলকের আয়তন $V = \frac{1}{3} \times \text{ভূমির ক্ষেত্রফল} \times \text{উচ্চতা}$।
@@ -2508,11 +2398,6 @@
           <t>ভেক্টর ট্রিপল প্রোডাক্টের বিখ্যাত সূত্র $\vec{A} \times (\vec{B} \times \vec{C}) = (\vec{A} \cdot \vec{C})\vec{B} - (\vec{A} \cdot \vec{B})\vec{C}$। জ্যামিতিকভাবে ব্যাখ্যা করো কেন এই ভেক্টরটি $\vec{B}$ এবং $\vec{C}$-এর সমতলে অবস্থিত এবং কেন ক্রস গুণন সংযোগ বিধি (Associative law) মেনে চলে না? অর্থাৎ $(\vec{A} \times \vec{B}) \times \vec{C} \neq \vec{A} \times (\vec{B} \times \vec{C})$ কেন?</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I26" t="inlineStr">
         <is>
           <t>১. ধরি $\vec{D} = \vec{B} \times \vec{C}$। $\vec{D}$ ভেক্টরটি $\vec{B}$ ও $\vec{C}$-এর সমতলের সাথে লম্ব।
@@ -2559,11 +2444,6 @@
       <c r="G27" t="inlineStr">
         <is>
           <t>মূলবিন্দুর সাপেক্ষে কোনো কণার অবস্থান ভেক্টর $\vec{r} = \hat{i} - 2\hat{j} + 3\hat{k}\text{ m}$ এবং প্রযুক্ত বল $\vec{F} = 2\hat{i} + 3\hat{j} - 4\hat{k}\text{ N}$। মূলবিন্দুর সাপেক্ষে টর্ক $\vec{\tau}_0$ নির্ণয় করো। যদি একটি নতুন বিন্দু $P(1, 1, 1)$-এর সাপেক্ষে টর্ক মাপা হয়, তবে টর্কের মান কীভাবে পরিবর্তিত হবে?</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2619,11 +2499,6 @@
           <t>একটি কেন্দ্রীয় বলের (Central force $\vec{F} = f(r)\hat{r}$) অধীনে গতিশীল গ্রহের ক্ষেত্রে প্রমাণ করো যে কৌণিক ভরবেগ $\vec{L} = \vec{r} \times \vec{p}$ সময়ের সাপেক্ষে একটি সংরক্ষিত ধ্রুব ভেক্টর। এর থেকে প্রমাণ করো যে গ্রহের কক্ষপথ সর্বদা একটি দ্বিমাত্রিক সমতলে আবদ্ধ থাকে এবং ক্ষেত্রীয় বেগ $\frac{d\vec{A}}{dt} = \frac{\vec{L}}{2m} = \text{ধ্রুবক}$ (কেপলারের ২য় সূত্র)।</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I28" t="inlineStr">
         <is>
           <t>১. কৌণিক ভরবেগের সময়ের সাপেক্ষে ব্যবকলন:
@@ -2675,11 +2550,6 @@
           <t>একটি ঘূর্ণায়মান দৃঢ় বস্তুর কৌণিক বেগ $\vec{\omega} = 2\hat{i} - 3\hat{j} + 4\hat{k}\text{ rad/s}$ এবং ঘূর্ণন অক্ষের সাপেক্ষে একটি কণার অবস্থান $\vec{r} = 3\hat{i} + 2\hat{j} - \hat{k}\text{ m}$। কণাটির রৈখিক বেগ $\vec{v} = \vec{\omega} \times \vec{r}$ নির্ণয় করো এবং প্রমাণ করো যে $\vec{v}$ ভেক্টরটি $\vec{\omega}$ এবং $\vec{r}$ উভয়ের ওপর লম্ব।</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I29" t="inlineStr">
         <is>
           <t>১. ক্রস গুণন:
@@ -2731,11 +2601,6 @@
           <t>যেকোনো তিনটি ভেক্টর $\vec{A}, \vec{B}, \vec{C}$-এর জন্য জ্যাকোবি আইডেন্টিটি হলো $\vec{A} \times (\vec{B} \times \vec{C}) + \vec{B} \times (\vec{C} \times \vec{A}) + \vec{C} \times (\vec{A} \times \vec{B}) = 0$। ভেক্টর ট্রিপল প্রোডাক্টের সূত্র ব্যবহার করে এই অভেদটি প্রমাণ করো। আধুনিক কোয়ান্টাম বলবিদ্যায় লি-বীজগণিতের (Lie Algebra) সাথে এর গুরুত্ব কী?</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I30" t="inlineStr">
         <is>
           <t>১. প্রথম পদ: $\vec{A} \times (\vec{B} \times \vec{C}) = (\vec{A} \cdot \vec{C})\vec{B} - (\vec{A} \cdot \vec{B})\vec{C}$
@@ -2786,11 +2651,6 @@
           <t>$I$ তড়িৎপ্রবাহ বহনকারী $A$ ক্ষেত্রফলের একটি ক্ষুদ্র সমতল লুপের চৌম্বক মোমেন্ট $\vec{m} = I \vec{A}$। সুষম চৌম্বক ক্ষেত্র $\vec{B}$-তে স্থাপিত হলে এর ওপর ক্রিয়াশীল টর্ক $\vec{\tau} = \vec{m} \times \vec{B}$ এবং স্থিতিশক্তি $U = -\vec{m} \cdot \vec{B}$। কোন ওরিয়েন্টেশনে লুপটি সুস্থিত সাম্যাবস্থায় (Stable equilibrium) থাকে?</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I31" t="inlineStr">
         <is>
           <t>১. টর্কের মান $\tau = m B \sin \theta$। সাম্যাবস্থার জন্য $\tau = 0 \implies \sin \theta = 0 \implies \theta = 0^\circ$ বা $180^\circ$।
@@ -2837,11 +2697,6 @@
       <c r="G32" t="inlineStr">
         <is>
           <t>$d$ প্রস্থের একটি নদীতে স্রোতের বেগ $u$ এবং শান্ত পানিতে নৌকার বেগ $v$। নদীটি সর্বনিম্ন সময়ে পার হতে হলে নৌকাকে কোন দিকে চালনা করতে হবে? এই ক্ষেত্রে নদী পার হতে প্রয়োজনীয় সময় $t_{\min}$ এবং নদীর স্রোতের দিকে অতিক্রান্ত পার্শ্বীয় দূরত্ব (Drift $x$) কত হবে?</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2946,11 +2801,6 @@
       <c r="G34" t="inlineStr">
         <is>
           <t>যখন স্রোতের বেগ নৌকার বেগের চেয়ে বেশি ($u &gt; v$), তখন সর্বনিম্ন ড্র্রিফট নিশ্চিত করতে নৌকাকে স্রোতের সাথে কোন কোণে চালাতে হবে? স্পর্শক জ্যামিতিক পদ্ধতি বা ক্যালকুলাস ব্যবহার করে দেখাও যে ন্যূনতম ড্র্রিফটের কোণ $\sin \theta = \frac{v}{u}$ (যেখানে $\theta$ উলম্বের সাথে কোণ) এবং সর্বনিম্ন ড্র্রিফট $x_{\min} = d \sqrt{\frac{u^2}{v^2} - 1}$।</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3006,11 +2856,6 @@
           <t>$w$ প্রস্থের একটি নদীতে স্রোতের বেগ তীরের কাছে শূন্য কিন্তু নদীর কেন্দ্রে সর্বোচ্চ, যা প্যারাবলিক সমীকরণ $u(y) = \frac{4 u_0}{w^2} y (w - y)$ মেনে চলে (যেখানে $y$ হলো তীর থেকে দূরত্ব)। একজন সাঁতারু সর্বদা নদীর বিপরীত তীরের দিকে লম্বভাবে স্থির দ্রুতি $v$-তে সাঁতার কাটলে অপর তীরে পৌঁছাতে সাঁতারুর মোট ড্র্রিফট কত হবে?</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I35" t="inlineStr">
         <is>
           <t>১. সাঁতারু লম্বভাবে সাঁতার কাটায় উলম্ব বেগ ধ্রুবক: $\frac{dy}{dt} = v \implies dt = \frac{dy}{v}$।
@@ -3059,11 +2904,6 @@
       <c r="G36" t="inlineStr">
         <is>
           <t>একটি সমবাহু ত্রিভুজ $ABC$-এর বাহুর দৈর্ঘ্য $L$। তিনটি কণা ত্রিভুজের তিন শীর্ষবিন্দুতে অবস্থান করছে। প্রতিটি কণা সর্বদা তার পরবর্তী কণাকে লক্ষ্য করে ধ্রুব দ্রুতি $v$-তে ধাবিত হয় ($A \to B, B \to C, C \to A$)। কণা তিনটি কখন এবং ত্রিভুজের কোন বিন্দুতে মিলিত হবে এবং মিলিত হওয়া পর্যন্ত প্রতিটি কণার অতিক্রান্ত দূরত্বের মান কত?</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3118,11 +2958,6 @@
           <t>$a$ বাহুবিশিষ্ট একটি বর্গের চার কোণায় চারটি কুকুর অবস্থান করছে। প্রত্যেকে তার পরবর্তী কুকুরকে লক্ষ্য করে ধ্রুব দ্রুতি $v$-তে দৌড়াতে শুরু করল। তারা কখন বর্গের কেন্দ্রে মিলিত হবে এবং প্রতিটি কুকুরের গতিপথ কেমন হবে?</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I37" t="inlineStr">
         <is>
           <t>১. বর্গের পরপর দুটি শীর্ষের সংযোগ রেখা পরস্পরের ওপর লম্ব ($90^\circ$)।
@@ -3173,11 +3008,6 @@
           <t>একটি নদীতে স্রোতের বেগ $u$। তীরের $A$ বিন্দু থেকে একটি নৌকা যাত্রা শুরু করল অপর তীরের ভাটিতে $L$ দূরত্বে অবস্থিত $B$ বিন্দুতে অপেক্ষমাণ একটি স্থির লঞ্চের কাছে পৌঁছাতে। যদি নৌকার নিজস্ব দ্রুতি $v$ হয়, তবে লঞ্চটিতে পৌঁছানোর জন্য ন্যূনতম সময় কত হবে এবং কোন কোণে যাত্রা করতে হবে?</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I38" t="inlineStr">
         <is>
           <t>১. নদী পারাপার ও ইন্টারসেপশনের জন্য লব্ধি বেগ ভেক্টর $\vec{v}_R = \vec{v} + \vec{u}$ অবশ্যই $AB$ সরলরেখা বরাবর পরিচালিত হতে হবে।
@@ -3227,11 +3057,6 @@
           <t>$w$ প্রস্থের একটি নদীতে স্রোতের বেগ $u$। একটি নৌকা এক তীর থেকে যাত্রা করে সর্বদা অপর তীরের একটি নির্দিষ্ট বিন্দু $O$-কে লক্ষ্য করে ধ্রুব দ্রুতি $v$ ($v = u$)-তে চালিত হচ্ছে। ডিফারেনশিয়াল সমীকরণ গঠন করে দেখাও যে নৌকার ট্রাজেক্টরি কেন একটি প্যারাবোলা বা ট্র্যাকট্রিক্স বক্ররেখা অনুসরণ করে এবং নৌকাটি কি কখনো $O$ বিন্দুতে পৌঁছাতে পারবে?</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I39" t="inlineStr">
         <is>
           <t>১. ধরি নৌকার অবস্থান $(x, y)$, যেখানে $O$ মূলবিন্দু $(0, 0)$।
@@ -3243,7 +3068,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>নৌকাটি $O$ বিন্দুতে পৌঁছাতে পারবে না; এটি তীরের সমান্তরালে $O$ বিন্দুর ভাটিতে $rac{w}{2}$ দূরত্বে গিয়ে তীরে ভিড়বে।</t>
+          <t>নৌকাটি $O$ বিন্দুতে পৌঁছাতে পারবে না; এটি তীরের সমান্তরালে $O$ বিন্দুর ভাটিতে $\frac{w}{2}$ দূরত্বে গিয়ে তীরে ভিড়বে।</t>
         </is>
       </c>
     </row>
@@ -3279,11 +3104,6 @@
       <c r="G40" t="inlineStr">
         <is>
           <t>দুটি কণা ১ ও ২ এর প্রাথমিক অবস্থান ভেক্টর যথাক্রমে $\vec{r}_1$ ও $\vec{r}_2$ এবং ধ্রুব বেগ যথাক্রমে $\vec{v}_1$ ও $\vec{v}_2$। কণা দুটির মধ্যে সরাসরি সংঘর্ষ ঘটার প্রয়োজনীয় ও পর্যাপ্ত ভেক্টর শর্তটি প্রতিপাদন করো এবং সংঘর্ষের সময় $t_c$ নির্ণয় করো।</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -3336,11 +3156,6 @@
           <t>একটি নদী পারাপারের সময় একটি নৌকা ন্যূনতম সময়ে ($t_1$) নদী পার হয় এবং অপর নৌকাটি ন্যূনতম পথে ($t_2$) নদী পার হয় ($v &gt; u$)। দেখাও যে শান্ত পানিতে নদী পার হতে প্রয়োজনীয় সময় $t_0$ হলে তাদের মধ্যে সম্পর্ক $t_0 = \sqrt{t_1 t_2}$।</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I41" t="inlineStr">
         <is>
           <t>১. নদীর প্রস্থ $d$। শান্ত পানিতে নদী পার হতে সময় $t_0 = \frac{d}{v}$।
@@ -3389,11 +3204,6 @@
       <c r="G42" t="inlineStr">
         <is>
           <t>বৃষ্টি উলম্বভাবে নিচের দিকে $v_r = 10\text{ m/s}$ বেগে পড়ছে। পূর্ব দিকে $v_w = 5\text{ m/s}$ বেগে বাতাস বইছে। একজন সাইকেল আরোহী উত্তর দিকে $v_c = 12\text{ m/s}$ বেগে সাইকেল চালাচ্ছেন। বৃষ্টি থেকে বাঁচতে তাকে উলম্বের সাথে কত কোণে এবং কোন দিকে ছাতা ধরতে হবে?</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3450,11 +3260,6 @@
           <t>বৃষ্টি উলম্বভাবে স্থির দ্রুতি $v_r$-তে পড়ছে। একজন পথচারী স্থির অবস্থা থেকে অনুভূমিক সরলরেখায় ধ্রুব ত্বরণ $a$-তে দৌড়াতে শুরু করলেন। $t$ সময় পর পথচারীর সাপেক্ষে বৃষ্টির আপাত কোণ $\theta(t)$ হলে দেখাও যে তাকে যে কৌণিক হারে ছাতা ঘোরাতে হবে তা $\frac{d\theta}{dt} = \frac{a v_r}{v_r^2 + a^2 t^2}$। কখন এই কৌণিক বেগ সর্বোচ্চ হয়?</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I43" t="inlineStr">
         <is>
           <t>১. $t$ সময় পর আরোহীর বেগ: $v_m(t) = a t$।
@@ -3503,11 +3308,6 @@
       <c r="G44" t="inlineStr">
         <is>
           <t>একজন লোক যখন $v_1 = 3\text{ km/h}$ বেগে হাঁটে তখন সে দেখে বৃষ্টি উলম্বভাবে পড়ছে। কিন্তু যখন সে তার বেগ দ্বিগুণ করে $v_2 = 6\text{ km/h}$ বেগে দৌড়ায় তখন সে দেখে বৃষ্টি উলম্বের সাথে $45^\circ$ কোণে আপতিত হচ্ছে। ভেক্টর সমীকরণের সাহায্যে বৃষ্টির প্রকৃত উলম্ব বেগ এবং অনুভূমিক বেগ নির্ণয় করো।</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3564,11 +3364,6 @@
           <t>অনুভূমিকের সাথে $\alpha = 30^\circ$ কোণে আনত একটি পাহাড়ি রাস্তা বেয়ে একজন সাইকেল আরোহী $u = 10\text{ m/s}$ বেগে ওপরে উঠছে। বৃষ্টি উলম্বভাবে নিচের দিকে $v = 10\sqrt{3}\text{ m/s}$ বেগে পড়ছে। আরোহীকে রাস্তার তলের সাথে কত কোণে ছাতা ধরতে হবে?</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I45" t="inlineStr">
         <is>
           <t>১. রাস্তার তলকে $x'$-অক্ষ এবং তার লম্বকে $y'$-অক্ষ ধরি।
@@ -3622,11 +3417,6 @@
           <t>একটি জাহাজ $A$ উত্তর দিকে $v_A = 20\text{ km/h}$ বেগে এবং অপর জাহাজ $B$ পশ্চিম দিকে $v_B = 20\text{ km/h}$ বেগে চলছে। কোনো এক মুহূর্তে $A$ জাহাজটি $B$ জাহাজের ঠিক দক্ষিণে $10\text{ km}$ দূরত্বে ছিল। জাহাজ দুটির মধ্যকার নিকটতম দূরত্ব (Closest approach distance $d_{\min}$) কত হবে এবং কত সময় পর তারা এই অবস্থানে পৌঁছাবে?</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I46" t="inlineStr">
         <is>
           <t>১. অবস্থান ভেক্টর: $B$-কে মূলবিন্দু $(0, 0)$ ধরলে $A$-এর অবস্থান $\vec{r}_A = -10\hat{j}$।
@@ -3678,11 +3468,6 @@
       <c r="G47" t="inlineStr">
         <is>
           <t>একটি গাড়ি উত্তর দিকে $v$ বেগে চলছে এবং বাতাসের আপাত অনুভূতি হচ্ছে উত্তর-পূর্ব দিক থেকে। গাড়িটি যখন একই বেগে বিপরীত দিকে (দক্ষিণে) ফিরে আসে তখন বাতাসের আপাত অনুভূতি হয় পূর্ব দিক থেকে। বাতাসের প্রকৃত বেগ ভেক্টর নির্ণয় করো।</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3740,11 +3525,6 @@
           <t>একটি বিমান ভূমির সাপেক্ষে সোজা উত্তর দিকে উড়ে যেতে চায়। বাতাসের বেগ পশ্চিম থেকে পূর্ব দিকে $u = 50\text{ km/h}$ এবং শান্ত বাতাসে বিমানের এয়ারস্পিড $v = 200\text{ km/h}$। বিমানচালককে কোন দিকে বিমান চালাতে হবে এবং ভূমির সাপেক্ষে বিমানের কার্যকর গ্রাউন্ডস্পিড কত হবে?</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I48" t="inlineStr">
         <is>
           <t>১. গ্রাউন্ড ভেলোসিটি $\vec{v}_g$ নিখুঁতভাবে উত্তরমুখী হতে হবে: $\vec{v}_g = v_g \hat{j}$।
@@ -3795,11 +3575,6 @@
       <c r="G49" t="inlineStr">
         <is>
           <t>একটি স্থির উত্তল দর্পণের ফোকাস দূরত্ব $f = 20\text{ cm}$। দর্পণের প্রধান অক্ষ বরাবর একটি বস্তু $u = -30\text{ cm}$ অবস্থান থেকে দর্পণের দিকে $v_o = 5\text{ m/s}$ ধ্রুব বেগে গতিশীল। এই মুহূর্তে বস্তুটির সাপেক্ষে তার প্রতিবিম্বের আপেক্ষিক বেগ কত?</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3856,11 +3631,6 @@
           <t>চিরায়ত আলোক অপেরণে (Stellar aberration) আপেক্ষিক বেগ $\vec{v}_{\text{rel}} = \vec{c} - \vec{v}_e$ দ্বারা ব্যাখ্যা করা হয়। কিন্তু আইনস্টাইনের বিশেষ আপেক্ষিকতায় সকল ফ্রেমে আলোর দ্রুতি ধ্রুবক $c$। আপেক্ষিকতার বেগ রূপান্তর নীতি প্রয়োগ করে কীভাবে লরেন্টজ কোণ রূপান্তর সমীকরণ $\cos \theta' = \frac{\cos \theta - v/c}{1 - \frac{v}{c}\cos \theta}$ পাওয়া যায়?</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I50" t="inlineStr">
         <is>
           <t>১. লরেন্টজ রূপান্তরে ফোটনের বেগ উপাংশ: $c_x = c \cos \theta, c_y = c \sin \theta$।
@@ -3907,11 +3677,6 @@
       <c r="G51" t="inlineStr">
         <is>
           <t>দুটি কণা মহাকাশে স্বাধীনভাবে চলছে। ১ম কণার গতি $\vec{r}_1(t) = (t)\hat{i} + (2t)\hat{j} + (3t)\hat{k}$ এবং ২য় কণার গতি $\vec{r}_2(t) = (1 + t)\hat{i} + (t^2)\hat{j} + (t)\hat{k}$। ক্যালকুলাস ও ভেক্টর দূরত্বের সমীকরণ ব্যবহার করে দেখাও যে কোন মুহূর্তে কণা দুটির মধ্যবর্তী দূরত্ব ন্যূনতম হবে?</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3949,7 +3714,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>ত্রিমাত্রিক ভেক্টর ও লব্ধির কোণ</t>
+          <t>ভেক্টর গুণন, অভিক্ষেপ ও স্কেলার ট্রিপল প্রোডাক্ট</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3962,31 +3727,25 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>##PRESET:vector-3d[size:medium]##
-একটি বিন্দুতে তিনটি বল $\vec{F}_1 = 2\hat{i} + 3\hat{j} - 4\hat{k}\text{{ N}}$, $\vec{F}_2 = -5\hat{i} + \hat{j} + 2\hat{k}\text{{ N}}$ এবং $\vec{F}_3 = \hat{i} - 6\hat{j} + 7\hat{k}\text{{ N}}$ যুগপৎ ক্রিয়াশীল। লব্ধি বলের মান এবং এটি $z$-অক্ষের ধনাত্মক দিকের সাথে কত কোণ উৎপন্ন করে নির্ণয় কর।</t>
+          <t>##PRESET:vector-addition[size:medium]##
+ভেক্টর $\vec{A} = 2\hat{i} + 3\hat{j} - 4\hat{k}$ এবং $\vec{B} = 4\hat{i} - 2\hat{j} + 3\hat{k}$। $\vec{A}$ ভেক্টরের ওপর $\vec{B}$ ভেক্টরের স্কেলার অভিক্ষেপ (Projection) এবং ভেক্টর উপাংশ (Component vector) নির্ণয় কর।</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>##PRESET:vector-3d[size:medium]##</t>
+          <t>##PRESET:vector-addition[size:medium]##</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>লব্ধি বল $\vec{R} = \vec{F}_1 + \vec{F}_2 + \vec{F}_3 = (2-5+1)\hat{i} + (3+1-6)\hat{j} + (-4+2+7)\hat{k} = -2\hat{i} - 2\hat{j} + 5\hat{k}\text{{ N}}$।
-মান $R = \sqrt{(-2)^2 + (-2)^2 + 5^2} = \sqrt{4 + 4 + 25} = \sqrt{33} \approx 5.74\text{{ N}}$।
-$z$-অক্ষের সাথে কোণ: $\cos\gamma = \frac{R_z}{R} = \frac{5}{\sqrt{33}} \approx 0.8704 \implies \gamma = \cos^{-1}(0.8704) \approx 46.12^\circ$।</t>
+          <t>$\vec{A} \cdot \vec{B} = (2)(4) + (3)(-2) + (-4)(3) = 8 - 6 - 12 = -10$। $|\vec{A}| = \sqrt{2^2 + 3^2 + (-4)^2} = \sqrt{4+9+16} = \sqrt{29}$। স্কেলার অভিক্ষেপ $= \frac{\vec{A} \cdot \vec{B}}{|\vec{A}|} = -\frac{10}{\sqrt{29}}$। ভেক্টর উপাংশ $= \left(\frac{\vec{A} \cdot \vec{B}}{|\vec{A}|^2}\right)\vec{A} = -\frac{10}{29}(2\hat{i} + 3\hat{j} - 4\hat{k})$।</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>$R = 5.74\text{{ N}}$, কোণ $\gamma = 46.12^\circ$</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
+          <t>স্কেলার অভিক্ষেপ $= -\frac{10}{\sqrt{29}}$, ভেক্টর উপাংশ $= -\frac{10}{29}(2\hat{i} + 3\hat{j} - 4\hat{k})$</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -4006,7 +3765,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>ঘনকের কর্ণদ্বয়ের মধ্যবর্তী কোণ</t>
+          <t>ভেক্টর গুণন, অভিক্ষেপ ও স্কেলার ট্রিপল প্রোডাক্ট</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -4019,33 +3778,25 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>##GEO:cube[s=5][size:small]##
-$a$ বাহুবিশিষ্ট একটি নিরেট ঘনকের দুটি প্রধান কর্ণের মধ্যবর্তী সূক্ষ্মকোণ ডট গুণনের সাহায্যে নির্ণয় কর।</t>
+          <t>##GEO:cube[s=4][size:small]##
+একটি নিরেট ঘনকের প্রতিটি বাহুর দৈর্ঘ্য $a$। ঘনকটির একটি শীর্ষ থেকে বিপরীত শীর্ষগামী প্রধান কর্ণ এবং একটি তল-কর্ণের (Face diagonal) মধ্যবর্তী কোণ ডট গুণনের সাহায্যে নির্ণয় কর।</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>##GEO:cube[s=5][size:small]##</t>
+          <t>##GEO:cube[s=4][size:small]##</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>ঘনকের মূলবিন্দু $(0,0,0)$ থেকে বিপরীত শীর্ষ $(a,a,a)$-এর কর্ণ ভেক্টর $\vec{d}_1 = a\hat{i} + a\hat{j} + a\hat{k}$।
-অন্য একটি শীর্ষ $(a,0,0)$ থেকে $(0,a,a)$-এর কর্ণ ভেক্টর $\vec{d}_2 = -a\hat{i} + a\hat{j} + a\hat{k}$।
-$\vec{d}_1 \cdot \vec{d}_2 = (a)(-a) + (a)(a) + (a)(a) = -a^2 + a^2 + a^2 = a^2$।
-মান $|\vec{d}_1| = \sqrt{a^2+a^2+a^2} = \sqrt{3}a$, $|\vec{d}_2| = \sqrt{3}a$।
-$\cos\theta = \frac{\vec{d}_1 \cdot \vec{d}_2}{|d_1||d_2|} = \frac{a^2}{3a^2} = \frac{1}{3} \implies \theta = \cos^{-1}\left(\frac{1}{3}\right) \approx 70.53^\circ$।</t>
+          <t>মূলবিন্দু $(0,0,0)$ হতে বিপরীত শীর্ষ $(a,a,a)$ গামী প্রধান কর্ণ $\vec{D} = a\hat{i} + a\hat{j} + a\hat{k}$ ($|\vec{D}| = \sqrt{3}a$)। $xy$-তলের কর্ণ $\vec{d} = a\hat{i} + a\hat{j}$ ($|\vec{d}| = \sqrt{2}a$)। $\vec{D} \cdot \vec{d} = a^2 + a^2 = 2a^2$। $\cos\theta = \frac{2a^2}{\sqrt{3}a \cdot \sqrt{2}a} = \frac{2}{\sqrt{6}} = \sqrt{\frac{2}{3}} \implies \theta \approx 35.26^\circ$।</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>$\theta = \cos^{-1}\left(\frac{1}{3}\right) \approx 70.53^\circ$</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
+          <t>$\theta = \cos^{-1}\left(\sqrt{\frac{2}{3}}\right) \approx 35.26^\circ$</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -4065,12 +3816,12 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>নদী-নৌকা ও ন্যূনতম বিচ্যুতি (Minimum Drift)</t>
+          <t>ভেক্টর গুণন, অভিক্ষেপ ও স্কেলার ট্রিপল প্রোডাক্ট</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>TOUGH</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -4078,33 +3829,25 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>##PRESET:vector-addition[size:medium]##
-একটি নদীর স্রোতের বেগ $u = 5\text{ km/h}$ এবং নৌকার স্থির পানিতে সর্বোচ্চ বেগ $v = 3\text{ km/h}$। নদীর প্রস্থ $d = 0.5\text{{ km}}$। যেহেতু $v &lt; u$, সোজাসোজি পার হওয়া অসম্ভব। নদীর অপর পাড়ে সর্বনিম্ন কত অনুভূমিক বিচ্যুতিতে (Minimum drift $x_{\min}$) নৌকাটি পৌঁছাতে পারবে এবং এর জন্য কত কোণে রওনা দিতে হবে?</t>
+          <t>##PRESET:vector-cross[size:medium]##
+একটি কণার অবস্থান ভেক্টর $\vec{r} = (3\hat{i} - 2\hat{j} + 4\hat{k})\text{ m}$ এর ওপর $\vec{F} = (5\hat{i} + 4\hat{j} - 2\hat{k})\text{ N}$ মানের একটি বল প্রযুক্ত হলো। মূলবিন্দুর সাপেক্ষে প্রযুক্ত টর্কের ভেক্টর রাশিমালা এবং এর মান নির্ণয় কর।</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>##PRESET:vector-addition[size:medium]##</t>
+          <t>##PRESET:vector-cross[size:medium]##</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>ন্যূনতম বিচ্যুতির শর্ত: $\cos\alpha = -\frac{v}{u} = -\frac{3}{5} = -0.6 \implies \alpha = 180^\circ - 53.13^\circ = 126.87^\circ$।
-প্রস্থ বরাবর বেগ $v_y = v\sin\alpha = 3\sin(126.87^\circ) = 3 \times 0.8 = 2.4\text{ km/h}$।
-নদী পার হতে সময় $t = \frac{d}{v_y} = \frac{0.5}{2.4} = \frac{5}{24}\text{{ h}}$।
-স্রোত বরাবর লব্ধি বেগ $v_x = u + v\cos\alpha = 5 + 3(-0.6) = 5 - 1.8 = 3.2\text{ km/h}$।
-$\therefore$ সর্বনিম্ন বিচ্যুতি $x = v_x t = 3.2 \times \frac{5}{24} = \frac{16}{24} = \frac{2}{3}\text{{ km}} \approx 666.67\text{{ m}}$।</t>
+          <t>টর্ক $\vec{\tau} = \vec{r} \times \vec{F} = \begin{vmatrix} \hat{i} &amp; \hat{j} &amp; \hat{k} \\ 3 &amp; -2 &amp; 4 \\ 5 &amp; 4 &amp; -2 \end{vmatrix} = \hat{i}(4 - 16) - \hat{j}(-6 - 20) + \hat{k}(12 - (-10)) = -12\hat{i} + 26\hat{j} + 22\hat{k}\text{ N}\cdot\text{m}$। মান $|\vec{\tau}| = \sqrt{(-12)^2 + 26^2 + 22^2} = \sqrt{144 + 676 + 484} = \sqrt{1304} \approx 36.11\text{ N}\cdot\text{m}$।</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>$x_{\min} = 0.667\text{{ km}} = 666.7\text{{ m}}$, কোণ $\alpha = 126.87^\circ$</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
+          <t>$\vec{\tau} = -12\hat{i} + 26\hat{j} + 22\hat{k}\text{ N}\cdot\text{m}, |\vec{\tau}| = 36.11\text{ N}\cdot\text{m}$</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -4124,46 +3867,38 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>ত্রিভুজের ক্ষেত্রফল ও একক লম্ব ভেক্টর</t>
+          <t>ভেক্টর গুণন, অভিক্ষেপ ও স্কেলার ট্রিপল প্রোডাক্ট</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>##GEO:triangle-altitude[A=A,B=B,C=C,D=D][size:small]##
-একটি ত্রিভুজের শীর্ষবিন্দু তিনটি যথাক্রমে $A(1, 2, 3)$, $B(2, -1, 1)$ এবং $C(-1, 2, -3)$। ভেক্টর পদ্ধতির সাহায্যে ত্রিভুজ $ABC$-এর ক্ষেত্রফল এবং ত্রিভুজটির তলের ওপর একটি একক লম্ব ভেক্টর নির্ণয় কর।</t>
+          <t>##GEO:triangle[a=3,b=4,c=4][size:small]##
+একটি ত্রিভুজের তিনটি শীর্ষবিন্দুর অবস্থান ভেক্টর যথাক্রমে $A(1, 2, 3)$, $B(2, -1, 1)$ এবং $C(-1, 2, 3)$ হলে ভেক্টর পদ্ধতির সাহায্যে ত্রিভুজ $ABC$-এর ক্ষেত্রফল নির্ণয় কর।</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>##GEO:triangle-altitude[A=A,B=B,C=C,D=D][size:small]##</t>
+          <t>##GEO:triangle[a=3,b=4,c=4][size:small]##</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>$\vec{AB} = (2-1)\hat{i} + (-1-2)\hat{j} + (1-3)\hat{k} = \hat{i} - 3\hat{j} - 2\hat{k}$।
-$\vec{AC} = (-1-1)\hat{i} + (2-2)\hat{j} + (-3-3)\hat{k} = -2\hat{i} + 0\hat{j} - 6\hat{k}$।
-$\vec{AB} \times \vec{AC} = \begin{vmatrix} \hat{i} &amp; \hat{j} &amp; \hat{k} \\ 1 &amp; -3 &amp; -2 \\ -2 &amp; 0 &amp; -6 \end{vmatrix} = \hat{i}(18 - 0) - \hat{j}(-6 - 4) + \hat{k}(0 - 6) = 18\hat{i} + 10\hat{j} - 6\hat{k}$।
-$|\vec{AB} \times \vec{AC}| = \sqrt{18^2 + 10^2 + (-6)^2} = \sqrt{324 + 100 + 36} = \sqrt{460} \approx 21.45$।
-ক্ষেত্রফল $= \frac{1}{2} |\vec{AB} \times \vec{AC}| \approx 10.72$ বর্গ একক।</t>
+          <t>বাহু $\vec{AB} = (2-1)\hat{i} + (-1-2)\hat{j} + (1-3)\hat{k} = \hat{i} - 3\hat{j} - 2\hat{k}$। বাহু $\vec{AC} = (-1-1)\hat{i} + (2-2)\hat{j} + (3-3)\hat{k} = -2\hat{i} + 0\hat{j} + 0\hat{k}$। $\vec{AB} \times \vec{AC} = \begin{vmatrix} \hat{i} &amp; \hat{j} &amp; \hat{k} \\ 1 &amp; -3 &amp; -2 \\ -2 &amp; 0 &amp; 0 \end{vmatrix} = \hat{i}(0) - \hat{j}(0 - 4) + \hat{k}(0 - 6) = 4\hat{j} - 6\hat{k}$। ক্ষেত্রফল $= \frac{1}{2}|\vec{AB} \times \vec{AC}| = \frac{1}{2}\sqrt{4^2 + (-6)^2} = \frac{1}{2}\sqrt{52} = \sqrt{13} \approx 3.61\text{ একক}$।</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>ক্ষেত্রফল $= 8.66\text{ sq. units}$, একক লম্ব ভেক্টর $\hat{n} = \frac{1}{\sqrt{300}}(8\hat{i} + 10\hat{j} + 6\hat{k})$</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
+          <t>ক্ষেত্রফল $= 3\sqrt{5}\text{ sq units} \approx 6.71\text{ একক}$</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -4183,45 +3918,38 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>কর্ণ দ্বারা সামান্তরিকের ক্ষেত্রফল</t>
+          <t>ভেক্টর গুণন, অভিক্ষেপ ও স্কেলার ট্রিপল প্রোডাক্ট</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>##GEO:parallelogram[A=A,B=B,C=C,D=D,b=6,h=4][size:small]##
-একটি সামান্তরিকের দুটি কর্ণ যথাক্রমে $\vec{d}_1 = 3\hat{i} + \hat{j} - 2\hat{k}$ এবং $\vec{d}_2 = \hat{i} - 3\hat{j} + 4\hat{k}$ নির্দেশ করে। সামান্তরিকটির ক্ষেত্রফল কত?</t>
+          <t>##PRESET:vector-addition[size:medium]##
+যদি $\vec{A} = 2\hat{i} + m\hat{j} - 3\hat{k}$ এবং $\vec{B} = 6\hat{i} - 3\hat{j} - 9\hat{k}$ পরস্পর সমান্তরাল হয়, তবে $m$-এর মান কত? আবার $\vec{A}$ ও $\vec{B}$ লম্ব হওয়ার শর্তে $m$-এর মান কত?</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>##GEO:parallelogram[A=A,B=B,C=C,D=D,b=6,h=4][size:small]##</t>
+          <t>##PRESET:vector-addition[size:medium]##</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>কর্ণদ্বয় দেওয়া থাকলে ক্ষেত্রফল $A = \frac{1}{2} |\vec{d}_1 \times \vec{d}_2|$।
-$\vec{d}_1 \times \vec{d}_2 = \begin{vmatrix} \hat{i} &amp; \hat{j} &amp; \hat{k} \\ 3 &amp; 1 &amp; -2 \\ 1 &amp; -3 &amp; 4 \end{vmatrix} = \hat{i}(4 - 6) - \hat{j}(12 - (-2)) + \hat{k}(-9 - 1) = -2\hat{i} - 14\hat{j} - 10\hat{k}$।
-$|\vec{d}_1 \times \vec{d}_2| = \sqrt{(-2)^2 + (-14)^2 + (-10)^2} = \sqrt{4 + 196 + 100} = \sqrt{300} = 10\sqrt{3}$।
-$\therefore$ ক্ষেত্রফল $= \frac{1}{2}(10\sqrt{3}) = 5\sqrt{3} \approx 8.66$ বর্গ একক।</t>
+          <t>সমান্তরাল হওয়ার শর্ত: $\frac{A_x}{B_x} = \frac{A_y}{B_y} = \frac{A_z}{B_z} \implies \frac{2}{6} = \frac{m}{-3} = \frac{-3}{-9} \implies \frac{1}{3} = \frac{m}{-3} \implies m = -1$। লম্ব হওয়ার শর্ত: $\vec{A} \cdot \vec{B} = 0 \implies 2(6) + m(-3) + (-3)(-9) = 0 \implies 12 - 3m + 27 = 0 \implies 3m = 39 \implies m = 13$।</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>$5\sqrt{3} \approx 8.66\text{ sq. units}$</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
+          <t>সমান্তরাল হলে $m = -1$, লম্ব হলে $m = 13$</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -4241,7 +3969,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>বৃষ্টি ও বাতাসের আপেক্ষিক বেগ</t>
+          <t>ভেক্টর গুণন, অভিক্ষেপ ও স্কেলার ট্রিপল প্রোডাক্ট</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -4254,32 +3982,25 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>##PRESET:vector-addition[size:medium]##
-উল্লম্বভাবে খাড়া নিচের দিকে $6\text{ m/s}$ বেগে বৃষ্টি পড়ছে এবং পূর্ব হতে পশ্চিমে $8\text{ m/s}$ বেগে বাতাস বইছে। একজন সাইকেল আরোহী পশ্চিম হতে পূর্বে $2\text{ m/s}$ বেগে চালালে তাকে উলম্বের সাথে কত কোণে ছাতা ধরতে হবে?</t>
+          <t>##GEO:parallelogram[w=4,h=3,angle=60][size:small]##
+একটি সামান্তরিকের দুটি সন্নিহিত বাহু $\vec{P} = 3\hat{i} - \hat{j} + 2\hat{k}$ এবং $\vec{Q} = \hat{i} + 2\hat{j} - 4\hat{k}$ দ্বারা সূচিত হলে সামান্তরিকটির কর্ণদ্বয়ের ভেক্টর রাশিমালা এবং তাদের মধ্যবর্তী সূক্ষ্মকোণ নির্ণয় কর।</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>##PRESET:vector-addition[size:medium]##</t>
+          <t>##GEO:parallelogram[w=4,h=3,angle=60][size:small]##</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>বৃষ্টির বেগ $\vec{v}_r = -6\hat{j}$। বাতাসের বেগ $\vec{v}_w = -8\hat{i}$। কার্যকর বৃষ্টির বেগ $\vec{v}_{rw} = -8\hat{i} - 6\hat{j}$।
-সাইকেলের বেগ $\vec{v}_c = +2\hat{i}$।
-আপেক্ষিক বেগ $\vec{v}_{rel} = \vec{v}_{rw} - \vec{v}_c = (-8\hat{i} - 6\hat{j}) - 2\hat{i} = -10\hat{i} - 6\hat{j}$।
-উলম্বের সাথে কোণ $\tan\theta = \frac{|v_x|}{|v_y|} = \frac{10}{6} = 1.667 \implies \theta = 59.04^\circ$।</t>
+          <t>কর্ণ $\vec{D}_1 = \vec{P} + \vec{Q} = 4\hat{i} + \hat{j} - 2\hat{k}$ ($|\vec{D}_1| = \sqrt{16+1+4} = \sqrt{21}$)। কর্ণ $\vec{D}_2 = \vec{P} - \vec{Q} = 2\hat{i} - 3\hat{j} + 6\hat{k}$ ($|\vec{D}_2| = \sqrt{4+9+36} = 7$)। $\vec{D}_1 \cdot \vec{D}_2 = 4(2) + 1(-3) + (-2)(6) = 8 - 3 - 12 = -7$। $\cos\theta = \frac{|-7|}{7\sqrt{21}} = \frac{1}{\sqrt{21}} \implies \theta = \cos^{-1}\left(\frac{1}{\sqrt{21}}\right) \approx 77.4^\circ$।</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>$\theta = 59.04^\circ$ উলম্বের সাথে পূর্ব দিকে</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
+          <t>$\vec{D}_1 = 4\hat{i}+\hat{j}-2\hat{k}, \vec{D}_2 = 2\hat{i}-3\hat{j}+6\hat{k}, \theta \approx 72.8^\circ$</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -4299,39 +4020,38 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>কোপ্ল্যানার ভেক্টর ও সমতলীয়তার শর্ত</t>
+          <t>ভেক্টর গুণন, অভিক্ষেপ ও স্কেলার ট্রিপল প্রোডাক্ট</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>যদি $\vec{A} = 2\hat{i} - \hat{j} + \hat{k}$, $\vec{B} = \hat{i} + 2\hat{j} - 3\hat{k}$ এবং $\vec{C} = 3\hat{i} + p\hat{j} + 5\hat{k}$ ভেক্টর তিনটি একই সমতলে অবস্থান করে, তবে $p$-এর মান কত?</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr"/>
+          <t>##PRESET:vector-addition[size:medium]##
+যদি $|ec{A} + ec{B}| = |ec{A} - ec{B}|$ হয়, তবে প্রমাণ কর যে $ec{A}$ এবং $ec{B}$ পরস্পর লম্ব। যদি $|ec{A} + ec{B}| = \sqrt{3}|ec{A} - ec{B}|$ এবং $|ec{A}| = |ec{B}|$ হয়, তবে ভেক্টরদ্বয়ের মধ্যবর্তী কোণ কত?</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>##PRESET:vector-addition[size:medium]##</t>
+        </is>
+      </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>সমতলীয় হওয়ার শর্ত: স্কেলার ট্রিপল প্রোডাক্ট $\vec{A} \cdot (\vec{B} \times \vec{C}) = 0$।
-$\begin{vmatrix} 2 &amp; -1 &amp; 1 \\ 1 &amp; 2 &amp; -3 \\ 3 &amp; p &amp; 5 \end{vmatrix} = 2(10 + 3p) + 1(5 + 9) + 1(p - 6) = 0$
-$\implies 20 + 6p + 14 + p - 6 = 0 \implies 7p + 28 = 0 \implies p = -4$।</t>
+          <t>$|\vec{A}+\vec{B}|^2 = |\vec{A}-\vec{B}|^2 \implies A^2 + B^2 + 2AB\cos\theta = A^2 + B^2 - 2AB\cos\theta \implies 4AB\cos\theta = 0 \implies \theta = 90^\circ$। দ্বিতীয় ক্ষেত্রে: $A^2 + A^2 + 2A^2\cos\theta = 3(A^2 + A^2 - 2A^2\cos\theta) \implies 2A^2(1+\cos\theta) = 6A^2(1-\cos\theta) \implies 1+\cos\theta = 3 - 3\cos\theta \implies 4\cos\theta = 2 \implies \cos\theta = 1/2 \implies \theta = 60^\circ$।</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>$p = -4$</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
+          <t>$\theta_1 = 90^\circ, \theta_2 = 60^\circ$</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -4351,38 +4071,38 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>কাজ ও স্কেলার গুণফল</t>
+          <t>ভেক্টর গুণন, অভিক্ষেপ ও স্কেলার ট্রিপল প্রোডাক্ট</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>EASY</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>একটি কণার ওপর $\vec{F} = (4\hat{i} + 2\hat{j} - 3\hat{k})\text{{ N}}$ বল প্রয়োগের ফলে কণাটি বিন্দু $P(1, 2, -1)$ হতে $Q(3, 0, 2)$-এ স্থানান্তরিত হয়। কৃতকাজের মান কত?</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr"/>
+          <t>##PRESET:vector-addition[size:medium]##
+একটি কণার ওপর তিনটি ধ্রুব বল $ec{F}_1 = 2\hat{i} + 3\hat{j} - \hat{k}$, $ec{F}_2 = -\hat{i} + 2\hat{j} + 4\hat{k}$ এবং $ec{F}_3 = 3\hat{i} - \hat{j} + 2\hat{k}$ ক্রিয়ারত। বলগুলোর সম্মিলিত প্রভাবে কণাটি বিন্দু $P(1, -2, 3)$ হতে $Q(4, 1, 2)$ তে স্থানান্তরিত হলে মোট কৃতকাজের পরিমাণ নির্ণয় কর।</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>##PRESET:vector-addition[size:medium]##</t>
+        </is>
+      </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>সরণ $\vec{s} = \vec{r}_Q - \vec{r}_P = (3-1)\hat{i} + (0-2)\hat{j} + (2 - (-1))\hat{k} = 2\hat{i} - 2\hat{j} + 3\hat{k}\text{{ m}}$।
-কাজ $W = \vec{F} \cdot \vec{s} = (4)(2) + (2)(-2) + (-3)(3) = 8 - 4 - 9 = -5\text{{ J}}$।</t>
+          <t>লব্ধি বল $\vec{F} = \vec{F}_1 + \vec{F}_2 + \vec{F}_3 = (2-1+3)\hat{i} + (3+2-1)\hat{j} + (-1+4+2)\hat{k} = 4\hat{i} + 4\hat{j} + 5\hat{k}\text{ N}$। সরণ $\vec{d} = \vec{r}_Q - \vec{r}_P = (4-1)\hat{i} + (1-(-2))\hat{j} + (2-3)\hat{k} = 3\hat{i} + 3\hat{j} - \hat{k}\text{ m}$। কৃতকাজ $W = \vec{F} \cdot \vec{d} = 4(3) + 4(3) + 5(-1) = 12 + 12 - 5 = 19\text{ J}$।</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>$-5\text{{ J}}$</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
+          <t>মোট কাজ $W = 16\text{ J}$</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -4402,38 +4122,39 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>টর্ক ও ভেক্টর গুণফল</t>
+          <t>ভেক্টর গুণন, অভিক্ষেপ ও স্কেলার ট্রিপল প্রোডাক্ট</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>মূলবিন্দুর সাপেক্ষে $\vec{r} = (3\hat{i} + 2\hat{j} - 4\hat{k})\text{{ m}}$ অবস্থানে ক্রিয়াশীল একটি বল $\vec{F} = (5\hat{i} - 3\hat{j} + 2\hat{k})\text{{ N}}$ হলে মূলবিন্দুর সাপেক্ষে প্রযুক্ত টর্কের মান নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr"/>
+          <t>##PRESET:vector-addition[size:medium]##
+কোনো বল ক্ষেত্রে বিভব শক্তি অপেক্ষক $U(x, y, z) = 3x^2 y - y z^2 + 4z$ জুল। বিন্দু $(1, -2, 1)$ মিটারে কণাটির ওপর প্রযুক্ত সংরক্ষণশীল বল $ec{F} = -
+abla U$ এবং এর মান নির্ণয় কর।</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>##PRESET:vector-addition[size:medium]##</t>
+        </is>
+      </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>টর্ক $\vec{\tau} = \vec{r} \times \vec{F} = \begin{vmatrix} \hat{i} &amp; \hat{j} &amp; \hat{k} \\ 3 &amp; 2 &amp; -4 \\ 5 &amp; -3 &amp; 2 \end{vmatrix} = \hat{i}(4 - 12) - \hat{j}(6 - (-20)) + \hat{k}(-9 - 10) = -8\hat{i} - 26\hat{j} - 19\hat{k}\text{{ N}}\cdot\text{{m}}$।
-মান $|\tau| = \sqrt{(-8)^2 + (-26)^2 + (-19)^2} = \sqrt{64 + 676 + 361} = \sqrt{1101} \approx 33.18\text{{ N}}\cdot\text{{m}}$।</t>
+          <t>$F_x = -\frac{\partial U}{\partial x} = -6xy$। $(1, -2, 1)$ বিন্দুতে $F_x = -6(1)(-2) = 12\text{ N}$। $F_y = -\frac{\partial U}{\partial y} = -(3x^2 - z^2) = -(3(1)^2 - 1^2) = -2\text{ N}$। $F_z = -\frac{\partial U}{\partial z} = -(-2yz + 4) = -(-2(-2)(1) + 4) = -(4+4) = -8\text{ N}$। বল $\vec{F} = 12\hat{i} - 2\hat{j} - 8\hat{k}\text{ N}$। মান $|\vec{F}| = \sqrt{144 + 4 + 64} = \sqrt{212} \approx 14.56\text{ N}$।</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>$\tau = 28.53\text{{ N}}\cdot\text{{m}}$</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
+          <t>$\vec{F} = 12\hat{i} - 2\hat{j} + 0\hat{k}\text{ N}, |\vec{F}| = 12.17\text{ N}$</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -4453,38 +4174,38 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>ভেক্টর বিভাজন ও উপাংশ বিশ্লেষণ 10</t>
+          <t>ভেক্টর গুণন, অভিক্ষেপ ও স্কেলার ট্রিপল প্রোডাক্ট</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>একটি বিন্দুতে $6\text{ N}$ এবং $4\text{ N}$ মানের দুটি বল পরস্পর $100^\circ$ কোণে ক্রিয়ারত। বলদ্বয়ের লব্ধির মান এবং ক্ষুদ্রতর বলটির সাথে লব্ধির উৎপন্ন কোণ নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr"/>
+          <t>##PRESET:vector-cross[size:medium]##
+তিনটি ভেক্টর $ec{A} = \hat{i} + 2\hat{j} + 3\hat{k}$, $ec{B} = 2\hat{i} - \hat{j} + \hat{k}$ এবং $ec{C} = 3\hat{i} + \hat{j} + 4\hat{k}$। ভেক্টর তিনটি সমতলীয় (Coplanar) কিনা তা স্কেলার ট্রিপল প্রোডাক্ট $ec{A} \cdot (ec{B} 	imes ec{C})$ নির্ণয়ের মাধ্যমে যাচাই কর।</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>##PRESET:vector-cross[size:medium]##</t>
+        </is>
+      </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>$R = \sqrt{6^2 + 4^2 + 2(6)(4)\cos(100^\circ)} = 6.61\text{ N}$।
-$\tan\theta = \frac{4\sin 100^\circ}{6 + 4\cos 100^\circ} \implies \theta = 36.59^\circ$।</t>
+          <t>স্কেলার ট্রিপল গুণন: $\begin{vmatrix} 1 &amp; 2 &amp; 3 \\ 2 &amp; -1 &amp; 1 \\ 3 &amp; 1 &amp; 4 \end{vmatrix} = 1(-4 - 1) - 2(8 - 3) + 3(2 - (-3)) = 1(-5) - 2(5) + 3(5) = -5 - 10 + 15 = 0$। যেহেতু ট্রিপল গুণফলের মান শূন্য, সুতরাং ভেক্টর তিনটি একই সমতলে অবস্থিত।</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>$R = 6.61\text{ N}, \theta = 36.59^\circ$</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
+          <t>$\vec{A} \cdot (\vec{B} \times \vec{C}) = 0$, ভেক্টর তিনটি সমতলীয়</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -4504,38 +4225,38 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>ভেক্টর বিভাজন ও উপাংশ বিশ্লেষণ 11</t>
+          <t>সামান্তরিক সূত্র ও বলের সাম্যাবস্থা</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>একটি বিন্দুতে $7\text{ N}$ এবং $5\text{ N}$ মানের দুটি বল পরস্পর $107^\circ$ কোণে ক্রিয়ারত। বলদ্বয়ের লব্ধির মান এবং ক্ষুদ্রতর বলটির সাথে লব্ধির উৎপন্ন কোণ নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr"/>
+          <t>##GEO:right-triangle[a=5,b=12,c=13][size:small]##
+দুটি বলের বৃহত্তম লব্ধি $17	ext{ N}$ এবং ক্ষুদ্রতম লব্ধি $7	ext{ N}$। বল দুটি পরস্পর সমকোণে ক্রিয়ারত হলে তাদের লব্ধির মান কত হবে?</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>##GEO:right-triangle[a=5,b=12,c=13][size:small]##</t>
+        </is>
+      </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>$R = \sqrt{7^2 + 5^2 + 2(7)(5)\cos(107^\circ)} = 7.32\text{ N}$।
-$\tan\theta = \frac{5\sin 107^\circ}{7 + 5\cos 107^\circ} \implies \theta = 40.81^\circ$।</t>
+          <t>$P + Q = 17$ এবং $P - Q = 7 \implies 2P = 24 \implies P = 12\text{ N}, Q = 5\text{ N}$। পরস্পর সমকোণে ($\alpha = 90^\circ$): $R = \sqrt{P^2 + Q^2} = \sqrt{12^2 + 5^2} = \sqrt{144 + 25} = \sqrt{169} = 13\text{ N}$।</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>$R = 7.32\text{ N}, \theta = 40.81^\circ$</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
+          <t>$R = 13\text{ N}$</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -4555,43 +4276,38 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>ভেক্টর বিভাজন ও উপাংশ বিশ্লেষণ 12</t>
+          <t>সামান্তরিক সূত্র ও বলের সাম্যাবস্থা</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>##PRESET:vector-addition[size:medium]##
-একটি বিন্দুতে $8\text{ N}$ এবং $6\text{ N}$ মানের দুটি বল পরস্পর $114^\circ$ কোণে ক্রিয়ারত। বলদ্বয়ের লব্ধির মান এবং ক্ষুদ্রতর বলটির সাথে লব্ধির উৎপন্ন কোণ নির্ণয় কর।</t>
+          <t>##GEO:parallelogram[w=4,h=3,angle=60][size:small]##
+একটি বিন্দুতে ক্রিয়ারত দুটি বল $P$ এবং $Q$-এর মধ্যবর্তী কোণ $lpha$। যদি বলদ্বয়ের লব্ধি $R = \sqrt{3}Q$ হয় এবং তা $P$-এর ক্রিয়ারেখার সাথে $30^\circ$ কোণ উৎপন্ন করে, তবে প্রমাণ কর যে $P = Q$ অথবা $P = 2Q$।</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>##PRESET:vector-addition[size:medium]##</t>
+          <t>##GEO:parallelogram[w=4,h=3,angle=60][size:small]##</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>$R = \sqrt{8^2 + 6^2 + 2(8)(6)\cos(114^\circ)} = 7.81\text{ N}$।
-$\tan\theta = \frac{6\sin 114^\circ}{8 + 6\cos 114^\circ} \implies \theta = 44.59^\circ$।</t>
+          <t>$\tan 30^\circ = \frac{Q\sin\alpha}{P + Q\cos\alpha} \implies \frac{1}{\sqrt{3}} = \frac{Q\sin\alpha}{P+Q\cos\alpha} \implies P + Q\cos\alpha = \sqrt{3}Q\sin\alpha$। আবার $R^2 = P^2 + Q^2 + 2PQ\cos\alpha = 3Q^2$। সমীকরণদ্বয় সমাধান করে পাওয়া যায় $P = Q$ অথবা $P = 2Q$।</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>$R = 7.81\text{ N}, \theta = 44.59^\circ$</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
+          <t>$P = Q$ অথবা $P = 2Q$</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -4611,38 +4327,38 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>ভেক্টর বিভাজন ও উপাংশ বিশ্লেষণ 13</t>
+          <t>সামান্তরিক সূত্র ও বলের সাম্যাবস্থা</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>একটি বিন্দুতে $9\text{ N}$ এবং $7\text{ N}$ মানের দুটি বল পরস্পর $121^\circ$ কোণে ক্রিয়ারত। বলদ্বয়ের লব্ধির মান এবং ক্ষুদ্রতর বলটির সাথে লব্ধির উৎপন্ন কোণ নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr"/>
+          <t>##GEO:triangle[a=4,b=4,c=4][size:small]##
+একটি কণার ওপর সমমানের তিনটি বল $10	ext{ N}$ ক্রিয়ারত থেকে কণাটিকে সাম্যাবস্থায় রেখেছে। লামির উপপাদ্যের সাহায্যে বলগুলোর মধ্যবর্তী কোণ নির্ণয় কর।</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>##GEO:triangle[a=4,b=4,c=4][size:small]##</t>
+        </is>
+      </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>$R = \sqrt{9^2 + 7^2 + 2(9)(7)\cos(121^\circ)} = 8.07\text{ N}$।
-$\tan\theta = \frac{7\sin 121^\circ}{9 + 7\cos 121^\circ} \implies \theta = 48.04^\circ$।</t>
+          <t>লামির উপপাদ্য: $\frac{P}{\sin\alpha} = \frac{Q}{\sin\beta} = \frac{R}{\sin\gamma}$। যেহেতু $P = Q = R = 10\text{ N}$, তাই $\sin\alpha = \sin\beta = \sin\gamma$। যেহেতু $\alpha + \beta + \gamma = 360^\circ$, সুতরাং প্রতি জোড়া বলের মধ্যবর্তী কোণ $\alpha = \beta = \gamma = \frac{360^\circ}{3} = 120^\circ$।</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>$R = 8.07\text{ N}, \theta = 48.04^\circ$</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
+          <t>প্রতিটি কোণ $= 120^\circ$</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -4662,38 +4378,38 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>ভেক্টর বিভাজন ও উপাংশ বিশ্লেষণ 14</t>
+          <t>সামান্তরিক সূত্র ও বলের সাম্যাবস্থা</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>একটি বিন্দুতে $3\text{ N}$ এবং $8\text{ N}$ মানের দুটি বল পরস্পর $128^\circ$ কোণে ক্রিয়ারত। বলদ্বয়ের লব্ধির মান এবং ক্ষুদ্রতর বলটির সাথে লব্ধির উৎপন্ন কোণ নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr"/>
+          <t>##PRESET:vector-addition[size:medium]##
+একটি বিন্দুতে ক্রিয়ারত দুটি বল $P$ এবং $2P$ এর লব্ধি $R$। যদি প্রথম বলটিকে দ্বিগুণ করা হয় এবং দ্বিতীয়টির মান $8	ext{ N}$ বৃদ্ধি করা হয়, তবে লব্ধির দিক অপরিবর্তিত থাকে। $P$-এর মান নির্ণয় কর।</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>##PRESET:vector-addition[size:medium]##</t>
+        </is>
+      </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>$R = \sqrt{3^2 + 8^2 + 2(3)(8)\cos(128^\circ)} = 6.59\text{ N}$।
-$\tan\theta = \frac{8\sin 128^\circ}{3 + 8\cos 128^\circ} \implies \theta = 106.98^\circ$।</t>
+          <t>লব্ধির দিক $\tan\theta = \frac{2P\sin\alpha}{P + 2P\cos\alpha} = \frac{2\sin\alpha}{1 + 2\cos\alpha}$। দ্বিতীয় ক্ষেত্রে: $\tan\theta = \frac{(2P+8)\sin\alpha}{2P + (2P+8)\cos\alpha}$। সমীকৃত করে: $\frac{2}{1+2\cos\alpha} = \frac{2P+8}{2P+(2P+8)\cos\alpha} \implies 4P + 2(2P+8)\cos\alpha = (2P+8) + 2(2P+8)\cos\alpha \implies 4P = 2P + 8 \implies 2P = 8 \implies P = 4\text{ N}$ (সঠিক সমাধান $P = 4\text{ N}$)।</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>$R = 6.59\text{ N}, \theta = 106.98^\circ$</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
+          <t>$P = 8\text{ N}$</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -4713,43 +4429,38 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>ভেক্টর বিভাজন ও উপাংশ বিশ্লেষণ 15</t>
+          <t>সামান্তরিক সূত্র ও বলের সাম্যাবস্থা</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>##PRESET:vector-addition[size:medium]##
-একটি বিন্দুতে $4\text{ N}$ এবং $4\text{ N}$ মানের দুটি বল পরস্পর $135^\circ$ কোণে ক্রিয়ারত। বলদ্বয়ের লব্ধির মান এবং ক্ষুদ্রতর বলটির সাথে লব্ধির উৎপন্ন কোণ নির্ণয় কর।</t>
+          <t>##GEO:parallelogram[w=5,h=3,angle=60][size:small]##
+দুটি বলের অনুপাত $3:5$ এবং তাদের লব্ধি $35	ext{ N}$। যদি বলদ্বয়ের অন্তর্গত কোণ $60^\circ$ হয়, তবে বল দুটির পৃথক মান নির্ণয় কর।</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>##PRESET:vector-addition[size:medium]##</t>
+          <t>##GEO:parallelogram[w=5,h=3,angle=60][size:small]##</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>$R = \sqrt{4^2 + 4^2 + 2(4)(4)\cos(135^\circ)} = 3.06\text{ N}$।
-$\tan\theta = \frac{4\sin 135^\circ}{4 + 4\cos 135^\circ} \implies \theta = 67.5^\circ$।</t>
+          <t>ধরি $P = 3x, Q = 5x$। $R = \sqrt{P^2 + Q^2 + 2PQ\cos 60^\circ} = \sqrt{9x^2 + 25x^2 + 2(15x^2)(0.5)} = \sqrt{34x^2 + 15x^2} = \sqrt{49x^2} = 7x$। দেওয়া আছে $7x = 35 \implies x = 5$। সুতরাং $P = 3(5) = 15\text{ N}$ এবং $Q = 5(5) = 25\text{ N}$।</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>$R = 3.06\text{ N}, \theta = 67.5^\circ$</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
+          <t>$P = 15\text{ N}, Q = 25\text{ N}$</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -4769,38 +4480,38 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>ভেক্টর বিভাজন ও উপাংশ বিশ্লেষণ 16</t>
+          <t>সামান্তরিক সূত্র ও বলের সাম্যাবস্থা</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>একটি বিন্দুতে $5\text{ N}$ এবং $5\text{ N}$ মানের দুটি বল পরস্পর $142^\circ$ কোণে ক্রিয়ারত। বলদ্বয়ের লব্ধির মান এবং ক্ষুদ্রতর বলটির সাথে লব্ধির উৎপন্ন কোণ নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr"/>
+          <t>##GEO:pendulum[angle=30,length=4][size:small]##
+একটি সুতার সাহায্যে $5	ext{ kg}$ ভরের একটি ধাতব গোলক ঝুলানো আছে। অনুভূমিকভাবে একটি বল $F$ প্রয়োগ করে সুতাটিকে উল্লম্বের সাথে $30^\circ$ কোণে স্থির রাখা হলো ($g = 9.8	ext{ ms}^{-2}$)। সুতার টান $T$ এবং প্রযুক্ত অনুভূমিক বল $F$ কত?</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>##GEO:pendulum[angle=30,length=4][size:small]##</t>
+        </is>
+      </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>$R = \sqrt{5^2 + 5^2 + 2(5)(5)\cos(142^\circ)} = 3.26\text{ N}$।
-$\tan\theta = \frac{5\sin 142^\circ}{5 + 5\cos 142^\circ} \implies \theta = 71.0^\circ$।</t>
+          <t>উল্লম্ব উপাংশ: $T\cos 30^\circ = mg = 5 \times 9.8 = 49\text{ N} \implies T = \frac{49}{\cos 30^\circ} = \frac{49}{0.866} \approx 56.58\text{ N}$। অনুভূমিক উপাংশ: $F = T\sin 30^\circ = 56.58 \times 0.5 = 28.29\text{ N}$।</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>$R = 3.26\text{ N}, \theta = 71.0^\circ$</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
+          <t>$T = 56.58\text{ N}, F = 28.29\text{ N}$</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -4820,38 +4531,38 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>ভেক্টর বিভাজন ও উপাংশ বিশ্লেষণ 17</t>
+          <t>সামান্তরিক সূত্র ও বলের সাম্যাবস্থা</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>একটি বিন্দুতে $6\text{ N}$ এবং $6\text{ N}$ মানের দুটি বল পরস্পর $149^\circ$ কোণে ক্রিয়ারত। বলদ্বয়ের লব্ধির মান এবং ক্ষুদ্রতর বলটির সাথে লব্ধির উৎপন্ন কোণ নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr"/>
+          <t>##PRESET:vector-addition[size:medium]##
+দুটি সমান মানের বল $P$ একটি বিন্দুতে ক্রিয়ারত। এদের মধ্যবর্তী কোণ কত হলে লব্ধির মান যেকোনো একটি বলের মানের সমান হবে?</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>##PRESET:vector-addition[size:medium]##</t>
+        </is>
+      </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>$R = \sqrt{6^2 + 6^2 + 2(6)(6)\cos(149^\circ)} = 3.21\text{ N}$।
-$\tan\theta = \frac{6\sin 149^\circ}{6 + 6\cos 149^\circ} \implies \theta = 74.5^\circ$।</t>
+          <t>$R^2 = P^2 + P^2 + 2P^2\cos\alpha$। দেওয়া আছে $R = P \implies P^2 = 2P^2 + 2P^2\cos\alpha \implies 2P^2(1+\cos\alpha) = P^2 \implies 1+\cos\alpha = 1/2 \implies \cos\alpha = -1/2 \implies \alpha = 120^\circ$।</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>$R = 3.21\text{ N}, \theta = 74.5^\circ$</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
+          <t>$\alpha = 120^\circ$</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -4871,21 +4582,21 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>ভেক্টর বিভাজন ও উপাংশ বিশ্লেষণ 18</t>
+          <t>সামান্তরিক সূত্র ও বলের সাম্যাবস্থা</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
           <t>##PRESET:vector-addition[size:medium]##
-একটি বিন্দুতে $7\text{ N}$ এবং $7\text{ N}$ মানের দুটি বল পরস্পর $36^\circ$ কোণে ক্রিয়ারত। বলদ্বয়ের লব্ধির মান এবং ক্ষুদ্রতর বলটির সাথে লব্ধির উৎপন্ন কোণ নির্ণয় কর।</t>
+কোনো বিন্দুতে ক্রিয়ারত দুটি বল $P$ এবং $Q$ এর লব্ধি $R$। যদি $Q$-কে বিপরীতমুখী করা হয়, তবে লব্ধির মান $S$ হয়। প্রমাণ কর যে $R^2 + S^2 = 2(P^2 + Q^2)$। যদি $R = 10	ext{ N}$ এবং $S = 6	ext{ N}$ হয়, তবে $\sqrt{P^2 + Q^2}$ এর মান কত?</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4895,19 +4606,14 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>$R = \sqrt{7^2 + 7^2 + 2(7)(7)\cos(36^\circ)} = 13.31\text{ N}$।
-$\tan\theta = \frac{7\sin 36^\circ}{7 + 7\cos 36^\circ} \implies \theta = 18.0^\circ$।</t>
+          <t>$R^2 = P^2 + Q^2 + 2PQ\cos\alpha$ এবং $S^2 = P^2 + Q^2 - 2PQ\cos\alpha$। যোগ করে: $R^2 + S^2 = 2(P^2 + Q^2)$। $10^2 + 6^2 = 100 + 36 = 136 = 2(P^2 + Q^2) \implies P^2 + Q^2 = 68 \implies \sqrt{P^2 + Q^2} = \sqrt{68} \approx 8.25\text{ N}$।</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>$R = 13.31\text{ N}, \theta = 18.0^\circ$</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
+          <t>$\sqrt{P^2 + Q^2} = \sqrt{68} \approx 8.25\text{ N}$</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -4927,38 +4633,38 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>ভেক্টর বিভাজন ও উপাংশ বিশ্লেষণ 19</t>
+          <t>সামান্তরিক সূত্র ও বলের সাম্যাবস্থা</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>একটি বিন্দুতে $8\text{ N}$ এবং $8\text{ N}$ মানের দুটি বল পরস্পর $43^\circ$ কোণে ক্রিয়ারত। বলদ্বয়ের লব্ধির মান এবং ক্ষুদ্রতর বলটির সাথে লব্ধির উৎপন্ন কোণ নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr"/>
+          <t>##GEO:right-triangle[a=3,b=5.2,angle=30][size:small]##
+একটি কাঠের ব্লককে একটি মসৃণ আনত তলে স্থির রাখা হয়েছে যার নতি কোণ $30^\circ$। ব্লকের ওজন $60	ext{ N}$ হলে আনত তল কর্তৃক ব্লকের ওপর প্রযুক্ত লম্ব প্রতিক্রিয়া বল এবং তল বরাবর নিম্নমুখী বলের উপাংশ কত?</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>##GEO:right-triangle[a=3,b=5.2,angle=30][size:small]##</t>
+        </is>
+      </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>$R = \sqrt{8^2 + 8^2 + 2(8)(8)\cos(43^\circ)} = 14.89\text{ N}$।
-$\tan\theta = \frac{8\sin 43^\circ}{8 + 8\cos 43^\circ} \implies \theta = 21.5^\circ$।</t>
+          <t>তল বরাবর উপাংশ $W_{parallel} = W\sin 30^\circ = 60 \times 0.5 = 30\text{ N}$। তলের লম্ব উপাংশ $W_{perp} = W\cos 30^\circ = 60 \times \frac{\sqrt{3}}{2} = 30\sqrt{3} \approx 51.96\text{ N}$। লম্ব প্রতিক্রিয়া $R_N = W_{perp} = 51.96\text{ N}$।</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>$R = 14.89\text{ N}, \theta = 21.5^\circ$</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
+          <t>লম্ব প্রতিক্রিয়া $R_N = 51.96\text{ N}$, তল বরাবর বল $F_{down} = 30.0\text{ N}$</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -4978,38 +4684,38 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>ভেক্টর বিভাজন ও উপাংশ বিশ্লেষণ 20</t>
+          <t>সামান্তরিক সূত্র ও বলের সাম্যাবস্থা</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>একটি বিন্দুতে $9\text{ N}$ এবং $4\text{ N}$ মানের দুটি বল পরস্পর $50^\circ$ কোণে ক্রিয়ারত। বলদ্বয়ের লব্ধির মান এবং ক্ষুদ্রতর বলটির সাথে লব্ধির উৎপন্ন কোণ নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr"/>
+          <t>##GEO:right-triangle[a=5,b=10.9,c=12][size:small]##
+একটি বিন্দুতে ক্রিয়ারত দুটি বল $12	ext{ N}$ এবং $5	ext{ N}$ এর লব্ধি ক্ষুদ্রতর বলটির সাথে সমকোণে থাকে। বলদ্বয়ের মধ্যবর্তী কোণ এবং লব্ধির মান নির্ণয় কর।</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>##GEO:right-triangle[a=5,b=10.9,c=12][size:small]##</t>
+        </is>
+      </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>$R = \sqrt{9^2 + 4^2 + 2(9)(4)\cos(50^\circ)} = 11.97\text{ N}$।
-$\tan\theta = \frac{4\sin 50^\circ}{9 + 4\cos 50^\circ} \implies \theta = 14.83^\circ$।</t>
+          <t>$\tan 90^\circ = \frac{12\sin\alpha}{5 + 12\cos\alpha} \implies 5 + 12\cos\alpha = 0 \implies \cos\alpha = -\frac{5}{12} \implies \alpha = \cos^{-1}(-0.4167) \approx 114.62^\circ$। লব্ধি $R = \sqrt{12^2 - 5^2} = \sqrt{144 - 25} = \sqrt{119} \approx 10.91\text{ N}$।</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>$R = 11.97\text{ N}, \theta = 14.83^\circ$</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
+          <t>$\alpha = 114.6^\circ, R = 10.91\text{ N}$</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -5029,21 +4735,21 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>ভেক্টর বিভাজন ও উপাংশ বিশ্লেষণ 21</t>
+          <t>নদী ও নৌকার গতি (River-Boat Relative Kinematics)</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
           <t>##PRESET:vector-addition[size:medium]##
-একটি বিন্দুতে $3\text{ N}$ এবং $5\text{ N}$ মানের দুটি বল পরস্পর $57^\circ$ কোণে ক্রিয়ারত। বলদ্বয়ের লব্ধির মান এবং ক্ষুদ্রতর বলটির সাথে লব্ধির উৎপন্ন কোণ নির্ণয় কর।</t>
+একটি নদীর প্রস্থ $d = 500	ext{ m}$ এবং স্রোতের বেগ $u = 3	ext{ km/h}$। একজন সাঁতারু স্থির পানিতে $v = 5	ext{ km/h}$ বেগে সাঁতার কাটতে পারেন। ঠিক সোজাসুজি অপর পাড়ে পৌঁছাতে হলে তাকে স্রোতের সাথে কত কোণে সাঁতার শুরু করতে হবে এবং নদী পার হতে কত সময় লাগবে?</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -5053,19 +4759,14 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>$R = \sqrt{3^2 + 5^2 + 2(3)(5)\cos(57^\circ)} = 7.1\text{ N}$।
-$\tan\theta = \frac{5\sin 57^\circ}{3 + 5\cos 57^\circ} \implies \theta = 36.23^\circ$।</t>
+          <t>সোজাসুজি পৌঁছানোর শর্ত: $\cos\alpha = -\frac{u}{v} = -\frac{3}{5} = -0.6 \implies \alpha = \cos^{-1}(-0.6) \approx 126.87^\circ$। কার্যকর লব্ধি বেগ $w = \sqrt{v^2 - u^2} = \sqrt{25 - 9} = 4\text{ km/h} = \frac{4 \times 1000}{3600} = \frac{10}{9}\text{ m/s}$। সময় $t = \frac{500}{10/9} = 450\text{ s} = 7.5\text{ min}$।</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>$R = 7.1\text{ N}, \theta = 36.23^\circ$</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
+          <t>কোণ $\alpha = 126.87^\circ$, সময় $t = 7.5\text{ মিনিট}$</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -5085,38 +4786,38 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>ভেক্টর বিভাজন ও উপাংশ বিশ্লেষণ 22</t>
+          <t>নদী ও নৌকার গতি (River-Boat Relative Kinematics)</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F73" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>একটি বিন্দুতে $4\text{ N}$ এবং $6\text{ N}$ মানের দুটি বল পরস্পর $64^\circ$ কোণে ক্রিয়ারত। বলদ্বয়ের লব্ধির মান এবং ক্ষুদ্রতর বলটির সাথে লব্ধির উৎপন্ন কোণ নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr"/>
+          <t>##PRESET:vector-addition[size:medium]##
+একটি নদীর প্রস্থ $800	ext{ m}$ এবং স্রোতের বেগ $4	ext{ m/s}$। একটি মোটর বোটের পানিতে নিজস্ব বেগ $6	ext{ m/s}$। বোটটি ন্যূনতম সময়ে নদী পার হতে চাইলে নদী পার হতে কত সেকেন্ড সময় লাগবে এবং এই সময় বোটটির ভাটির দিকে পার্শ্বীয় বিচ্যুতি (Drift) কত হবে?</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>##PRESET:vector-addition[size:medium]##</t>
+        </is>
+      </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>$R = \sqrt{4^2 + 6^2 + 2(4)(6)\cos(64^\circ)} = 8.55\text{ N}$।
-$\tan\theta = \frac{6\sin 64^\circ}{4 + 6\cos 64^\circ} \implies \theta = 39.12^\circ$।</t>
+          <t>ন্যূনতম সময়ের জন্য বোটকে নদীর সাথে লম্বভাবে চালাতে হবে ($\alpha = 90^\circ$)। $t_{\min} = \frac{d}{v} = \frac{800}{6} = 133.33\text{ s}$। স্রোতের টানে বিচ্যুতি $x = u \times t_{\min} = 4 \times 133.33 = 533.33\text{ m}$।</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>$R = 8.55\text{ N}, \theta = 39.12^\circ$</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
+          <t>ন্যূনতম সময় $t_{\min} = 133.33\text{ s}$, বিচ্যুতি $x = 533.33\text{ m}$</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -5136,38 +4837,38 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>ভেক্টর বিভাজন ও উপাংশ বিশ্লেষণ 23</t>
+          <t>নদী ও নৌকার গতি (River-Boat Relative Kinematics)</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>একটি বিন্দুতে $5\text{ N}$ এবং $7\text{ N}$ মানের দুটি বল পরস্পর $71^\circ$ কোণে ক্রিয়ারত। বলদ্বয়ের লব্ধির মান এবং ক্ষুদ্রতর বলটির সাথে লব্ধির উৎপন্ন কোণ নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr"/>
+          <t>##PRESET:vector-addition[size:medium]##
+একটি নদীর স্রোতের বেগ $u = 5	ext{ m/s}$ এবং সাঁতারুর সাঁতারের বেগ $v = 3	ext{ m/s}$ ($u &gt; v$ হওয়ায় সাঁতারুর পক্ষে ঠিক সোজাসুজি পৌঁছানো অসম্ভব)। নদী পার হতে সাঁতারু সর্বনিম্ন কত বিচ্যুতিতে (Minimum drift) অপর পাড়ে পৌঁছাতে পারবে এবং এর জন্য তাকে স্রোতের সাথে কত কোণে রওনা হতে হবে?</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>##PRESET:vector-addition[size:medium]##</t>
+        </is>
+      </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>$R = \sqrt{5^2 + 7^2 + 2(5)(7)\cos(71^\circ)} = 9.84\text{ N}$।
-$\tan\theta = \frac{7\sin 71^\circ}{5 + 7\cos 71^\circ} \implies \theta = 42.28^\circ$।</t>
+          <t>ন্যূনতম বিচ্যুতির শর্ত: $\cos\alpha = -\frac{v}{u} = -\frac{3}{5} \implies \alpha = 180^\circ - 36.87^\circ = 143.13^\circ$। বিচ্যুতি $x = d \frac{u + v\cos\alpha}{v\sin\alpha} = d \frac{5 + 3(-3/5)}{3(4/5)} = d \frac{5 - 1.8}{2.4} = d \frac{3.2}{2.4} = \frac{4}{3}d$। নদী প্রস্থ $d$ হলে বিচ্যুতি $\frac{4}{3}d$।</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>$R = 9.84\text{ N}, \theta = 42.28^\circ$</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
+          <t>সর্বনিম্ন বিচ্যুতি $x_{\min} = \frac{4}{3}d$, কোণ $\alpha = 143.13^\circ$</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -5187,21 +4888,21 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>ভেক্টর বিভাজন ও উপাংশ বিশ্লেষণ 24</t>
+          <t>নদী ও নৌকার গতি (River-Boat Relative Kinematics)</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
           <t>##PRESET:vector-addition[size:medium]##
-একটি বিন্দুতে $6\text{ N}$ এবং $8\text{ N}$ মানের দুটি বল পরস্পর $78^\circ$ কোণে ক্রিয়ারত। বলদ্বয়ের লব্ধির মান এবং ক্ষুদ্রতর বলটির সাথে লব্ধির উৎপন্ন কোণ নির্ণয় কর।</t>
+একটি নদীতে স্রোতের অনুকূলে একটি নৌকার বেগ $18	ext{ km/h}$ এবং প্রতিকূলে বেগ $6	ext{ km/h}$। স্থির পানিতে নৌকার বেগ এবং স্রোতের বেগ কত? নৌকাটি নদীটির প্রস্থ বরাবর ন্যূনতম পথে পার হতে চাইলে কত কোণে চালাতে হবে?</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5211,19 +4912,14 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>$R = \sqrt{6^2 + 8^2 + 2(6)(8)\cos(78^\circ)} = 10.95\text{ N}$।
-$\tan\theta = \frac{8\sin 78^\circ}{6 + 8\cos 78^\circ} \implies \theta = 45.6^\circ$।</t>
+          <t>$v + u = 18$ এবং $v - u = 6 \implies 2v = 24 \implies v = 12\text{ km/h}$, $u = 6\text{ km/h}$। ন্যূনতম পথে পার হওয়ার শর্ত: $\cos\alpha = -\frac{u}{v} = -\frac{6}{12} = -0.5 \implies \alpha = 120^\circ$।</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>$R = 10.95\text{ N}, \theta = 45.6^\circ$</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
+          <t>$v = 12\text{ km/h}, u = 6\text{ km/h}, \alpha = 120^\circ$</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -5243,38 +4939,38 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>ভেক্টর বিভাজন ও উপাংশ বিশ্লেষণ 25</t>
+          <t>নদী ও নৌকার গতি (River-Boat Relative Kinematics)</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>একটি বিন্দুতে $7\text{ N}$ এবং $4\text{ N}$ মানের দুটি বল পরস্পর $85^\circ$ কোণে ক্রিয়ারত। বলদ্বয়ের লব্ধির মান এবং ক্ষুদ্রতর বলটির সাথে লব্ধির উৎপন্ন কোণ নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr"/>
+          <t>##PRESET:vector-addition[size:medium]##
+একটি নদীর স্রোতের বেগ $2	ext{ m/s}$ এবং নদীর প্রস্থ $400	ext{ m}$। একটি নৌকা স্রোতের সাথে $60^\circ$ কোণে $4	ext{ m/s}$ বেগে যাত্রা শুরু করল। নদী পার হতে নৌকার কত সময় লাগবে এবং নদীর অপর পাড়ে যাত্রা বিন্দুর বিপরীত বিন্দুর সাপেক্ষে নৌকাটি কত দূরে পৌঁছাবে?</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>##PRESET:vector-addition[size:medium]##</t>
+        </is>
+      </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>$R = \sqrt{7^2 + 4^2 + 2(7)(4)\cos(85^\circ)} = 8.36\text{ N}$।
-$\tan\theta = \frac{4\sin 85^\circ}{7 + 4\cos 85^\circ} \implies \theta = 28.47^\circ$।</t>
+          <t>নদীর প্রস্থ বরাবর উপাংশ $v_y = v\sin 60^\circ = 4 \times \frac{\sqrt{3}}{2} = 2\sqrt{3}\text{ m/s}$। সময় $t = \frac{d}{v_y} = \frac{400}{2\sqrt{3}} = \frac{200}{\sqrt{3}} \approx 115.47\text{ s}$। অনুভূমিক লব্ধি বেগ $v_x = u + v\cos 60^\circ = 2 + 4(0.5) = 4\text{ m/s}$। দূরত্ব $x = v_x \times t = 4 \times 115.47 = 461.88\text{ m}$।</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>$R = 8.36\text{ N}, \theta = 28.47^\circ$</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
+          <t>সময় $t = 115.47\text{ s}$, দূরত্ব $x = 461.88\text{ m}$</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -5294,38 +4990,38 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>ভেক্টর বিভাজন ও উপাংশ বিশ্লেষণ 26</t>
+          <t>নদী ও নৌকার গতি (River-Boat Relative Kinematics)</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>একটি বিন্দুতে $8\text{ N}$ এবং $5\text{ N}$ মানের দুটি বল পরস্পর $92^\circ$ কোণে ক্রিয়ারত। বলদ্বয়ের লব্ধির মান এবং ক্ষুদ্রতর বলটির সাথে লব্ধির উৎপন্ন কোণ নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr"/>
+          <t>##PRESET:vector-addition[size:medium]##
+একজন মাঝি $1	ext{ km}$ প্রশস্ত নদীতে স্রোতের সাথে সমকোণে নৌকা চালিয়ে $15	ext{ মিনিটে}$ অপর পাড়ে পৌঁছায় এবং যাত্রা বিন্দুর বিপরীত বিন্দু হতে $750	ext{ m}$ দূরে অবতরণ করে। নৌকার বেগ এবং স্রোতের বেগ নির্ণয় কর।</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>##PRESET:vector-addition[size:medium]##</t>
+        </is>
+      </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>$R = \sqrt{8^2 + 5^2 + 2(8)(5)\cos(92^\circ)} = 9.28\text{ N}$।
-$\tan\theta = \frac{5\sin 92^\circ}{8 + 5\cos 92^\circ} \implies \theta = 32.56^\circ$।</t>
+          <t>সময় $t = 15\text{ min} = 0.25\text{ h}$। সমকোণে চালানোর ফলে $v = \frac{d}{t} = \frac{1\text{ km}}{0.25\text{ h}} = 4\text{ km/h}$। বিচ্যুতি $x = 0.75\text{ km}$। স্রোতের বেগ $u = \frac{x}{t} = \frac{0.75}{0.25} = 3\text{ km/h}$।</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>$R = 9.28\text{ N}, \theta = 32.56^\circ$</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
+          <t>নৌকার নিজস্ব বেগ $v = 4\text{ km/h}$, স্রোতের বেগ $u = 3\text{ km/h}$</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -5345,21 +5041,21 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>ভেক্টর বিভাজন ও উপাংশ বিশ্লেষণ 27</t>
+          <t>নদী ও নৌকার গতি (River-Boat Relative Kinematics)</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
           <t>##PRESET:vector-addition[size:medium]##
-একটি বিন্দুতে $9\text{ N}$ এবং $6\text{ N}$ মানের দুটি বল পরস্পর $99^\circ$ কোণে ক্রিয়ারত। বলদ্বয়ের লব্ধির মান এবং ক্ষুদ্রতর বলটির সাথে লব্ধির উৎপন্ন কোণ নির্ণয় কর।</t>
+একটি মোটর বোট একটি নদী আড়াআড়ি অতিক্রম করতে ন্যূনতম দূরত্বের পথে $t_1 = 10	ext{ মিনিটে}$ এবং ন্যূনতম সময়ের পথে $t_2 = 8	ext{ মিনিটে}$ নদী পার হয়। স্রোতের বেগ এবং বোটের বেগের অনুপাত $u/v$ নির্ণয় কর।</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5369,19 +5065,14 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>$R = \sqrt{9^2 + 6^2 + 2(9)(6)\cos(99^\circ)} = 10.01\text{ N}$।
-$\tan\theta = \frac{6\sin 99^\circ}{9 + 6\cos 99^\circ} \implies \theta = 36.32^\circ$।</t>
+          <t>ন্যূনতম দূরত্বে সময় $t_1 = \frac{d}{\sqrt{v^2 - u^2}}$। ন্যূনতম সময়ে $t_2 = \frac{d}{v}$। ভাগ করে: $\frac{t_2}{t_1} = \frac{\sqrt{v^2 - u^2}}{v} = \sqrt{1 - \frac{u^2}{v^2}} = \frac{8}{10} = 0.8$। বর্গ করে: $1 - \frac{u^2}{v^2} = 0.64 \implies \frac{u^2}{v^2} = 0.36 \implies \frac{u}{v} = 0.60$।</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>$R = 10.01\text{ N}, \theta = 36.32^\circ$</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
+          <t>$\frac{u}{v} = 0.60$</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -5401,38 +5092,38 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>ভেক্টর বিভাজন ও উপাংশ বিশ্লেষণ 28</t>
+          <t>নদী ও নৌকার গতি (River-Boat Relative Kinematics)</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F79" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>একটি বিন্দুতে $3\text{ N}$ এবং $7\text{ N}$ মানের দুটি বল পরস্পর $106^\circ$ কোণে ক্রিয়ারত। বলদ্বয়ের লব্ধির মান এবং ক্ষুদ্রতর বলটির সাথে লব্ধির উৎপন্ন কোণ নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr"/>
+          <t>##PRESET:vector-addition[size:medium]##
+একজন সাঁতারু নদীতে স্রোতের সাথে $120^\circ$ কোণে সাঁতার কেটে ঠিক অপর পাড়ে পৌঁছাল। যদি নদীর স্রোতের বেগ $1.5	ext{ m/s}$ হয়, তবে সাঁতারুর নিজস্ব সাঁতারের বেগ কত?</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>##PRESET:vector-addition[size:medium]##</t>
+        </is>
+      </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>$R = \sqrt{3^2 + 7^2 + 2(3)(7)\cos(106^\circ)} = 6.81\text{ N}$।
-$\tan\theta = \frac{7\sin 106^\circ}{3 + 7\cos 106^\circ} \implies \theta = 80.96^\circ$।</t>
+          <t>সোজাসুজি পৌঁছানোর শর্ত: $\cos 120^\circ = -\frac{u}{v} \implies -0.5 = -\frac{1.5}{v} \implies v = \frac{1.5}{0.5} = 3.0\text{ m/s}$।</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>$R = 6.81\text{ N}, \theta = 80.96^\circ$</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
+          <t>$v = 3.0\text{ m/s}$</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -5452,38 +5143,38 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>ভেক্টর বিভাজন ও উপাংশ বিশ্লেষণ 29</t>
+          <t>নদী ও নৌকার গতি (River-Boat Relative Kinematics)</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>একটি বিন্দুতে $4\text{ N}$ এবং $8\text{ N}$ মানের দুটি বল পরস্পর $113^\circ$ কোণে ক্রিয়ারত। বলদ্বয়ের লব্ধির মান এবং ক্ষুদ্রতর বলটির সাথে লব্ধির উৎপন্ন কোণ নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr"/>
+          <t>##PRESET:vector-addition[size:medium]##
+একটি নদীর পানি প্রবাহের বেগ $u = 3	ext{ m/s}$। একটি স্পিডবোটের বেগ $v = 5	ext{ m/s}$। বোটটি সোজাসুজি নদীর একপাড় থেকে অপরপাড়ে গিয়ে পুনরায় পূর্বের স্থানে ফিরে আসতে মোট সময় $T_1$ নেয়। একই দূরত্ব স্রোতের অনুকূলে গিয়ে প্রতিকূলে ফিরে আসতে সময় $T_2$ নিলে $T_1 / T_2$ অনুপাত কত?</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>##PRESET:vector-addition[size:medium]##</t>
+        </is>
+      </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>$R = \sqrt{4^2 + 8^2 + 2(4)(8)\cos(113^\circ)} = 7.42\text{ N}$।
-$\tan\theta = \frac{8\sin 113^\circ}{4 + 8\cos 113^\circ} \implies \theta = 83.23^\circ$।</t>
+          <t>নদী আড়াআড়ি যাওয়া-আসা: বেগ $w = \sqrt{5^2 - 3^2} = 4\text{ m/s}$, $T_1 = \frac{2d}{4} = 0.5d$। স্রোতের সমান্তরালে যাওয়া-আসা: $T_2 = \frac{d}{5+3} + \frac{d}{5-3} = \frac{d}{8} + \frac{d}{2} = \frac{5d}{8} = 0.625d$। অনুপাত $\frac{T_1}{T_2} = \frac{0.5}{0.625} = \frac{4}{5} = 0.80$।</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>$R = 7.42\text{ N}, \theta = 83.23^\circ$</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
+          <t>$T_1 / T_2 = 0.80$</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -5503,21 +5194,21 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>ভেক্টর বিভাজন ও উপাংশ বিশ্লেষণ 30</t>
+          <t>নদী ও নৌকার গতি (River-Boat Relative Kinematics)</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F81" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
           <t>##PRESET:vector-addition[size:medium]##
-একটি বিন্দুতে $5\text{ N}$ এবং $4\text{ N}$ মানের দুটি বল পরস্পর $120^\circ$ কোণে ক্রিয়ারত। বলদ্বয়ের লব্ধির মান এবং ক্ষুদ্রতর বলটির সাথে লব্ধির উৎপন্ন কোণ নির্ণয় কর।</t>
+নদীতে দুটি নৌকা একই বিন্দু হতে একই সময়ে বিপরীত পাড়ের দুটি নির্দিষ্ট বিন্দুর উদ্দেশ্যে রওনা হলো। প্রথমটি সোজাসুজি পথে এবং দ্বিতীয়টি ন্যূনতম সময়ের পথে। যদি উভয়ের পানিতে নিজস্ব বেগ $10	ext{ m/s}$ এবং স্রোত $6	ext{ m/s}$ হয়, তবে $1	ext{ মিনিট}$ পর তাদের মধ্যকার দূরত্ব কত?</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5527,19 +5218,14 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>$R = \sqrt{5^2 + 4^2 + 2(5)(4)\cos(120^\circ)} = 4.58\text{ N}$।
-$\tan\theta = \frac{4\sin 120^\circ}{5 + 4\cos 120^\circ} \implies \theta = 49.11^\circ$।</t>
+          <t>প্রথম নৌকার লব্ধি বেগ $w_1 = \sqrt{10^2 - 6^2} = 8\text{ m/s}$ সোজাসুজি $y$-অক্ষ বরাবর: $\vec{r}_1 = (0, 8 \times 60) = (0, 480)\text{ m}$। দ্বিতীয় নৌকা লম্বভাবে রওনা দেওয়ায় $v_y = 10\text{ m/s}, v_x = 6\text{ m/s}$: $\vec{r}_2 = (6 \times 60, 10 \times 60) = (360, 600)\text{ m}$। দূরত্ব $s = \sqrt{(360 - 0)^2 + (600 - 480)^2} = \sqrt{360^2 + 120^2} = \sqrt{129600 + 14400} = \sqrt{144000} \approx 379.47\text{ m}$।</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>$R = 4.58\text{ N}, \theta = 49.11^\circ$</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
+          <t>দূরত্ব $s = 480\text{ m}$</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -5559,38 +5245,38 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>ভেক্টর বিভাজন ও উপাংশ বিশ্লেষণ 31</t>
+          <t>নদী ও নৌকার গতি (River-Boat Relative Kinematics)</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>একটি বিন্দুতে $6\text{ N}$ এবং $5\text{ N}$ মানের দুটি বল পরস্পর $127^\circ$ কোণে ক্রিয়ারত। বলদ্বয়ের লব্ধির মান এবং ক্ষুদ্রতর বলটির সাথে লব্ধির উৎপন্ন কোণ নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr"/>
+          <t>##PRESET:vector-addition[size:medium]##
+একটি নদীর দুই পাড় সমান্তরাল। নদীর স্রোতের বেগ $2	ext{ km/h}$। একজন ব্যক্তি নদীর তীরের সাথে $30^\circ$ কোণে নৌকা চালিয়ে অপর পাড়ে পৌঁছাল। নদীর প্রস্থ $1	ext{ km}$ এবং নৌকার বেগ $4	ext{ km/h}$ হলে পারাপারে ব্যয়িত সময় ও লব্ধি বেগ নির্ণয় কর।</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>##PRESET:vector-addition[size:medium]##</t>
+        </is>
+      </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>$R = \sqrt{6^2 + 5^2 + 2(6)(5)\cos(127^\circ)} = 4.99\text{ N}$।
-$\tan\theta = \frac{5\sin 127^\circ}{6 + 5\cos 127^\circ} \implies \theta = 53.17^\circ$।</t>
+          <t>তীরের সাথে $30^\circ$ কোণ মানে স্রোতের সাথে কোণ $\alpha = 30^\circ$। উলম্ব উপাংশ $v_y = 4\sin 30^\circ = 2\text{ km/h}$। সময় $t = \frac{1\text{ km}}{2\text{ km/h}} = 0.5\text{ h} = 30\text{ min}$। লব্ধি বেগ $w = \sqrt{4^2 + 2^2 + 2(4)(2)\cos 30^\circ} = \sqrt{16 + 4 + 16(0.866)} = \sqrt{20 + 13.856} = \sqrt{33.856} \approx 5.82\text{ km/h}$।</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>$R = 4.99\text{ N}, \theta = 53.17^\circ$</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
+          <t>সময় $t = 30\text{ min}$, লব্ধি বেগ $w = 5.86\text{ km/h}$</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -5610,38 +5296,38 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>ভেক্টর বিভাজন ও উপাংশ বিশ্লেষণ 32</t>
+          <t>নদী ও নৌকার গতি (River-Boat Relative Kinematics)</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F83" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>একটি বিন্দুতে $7\text{ N}$ এবং $6\text{ N}$ মানের দুটি বল পরস্পর $134^\circ$ কোণে ক্রিয়ারত। বলদ্বয়ের লব্ধির মান এবং ক্ষুদ্রতর বলটির সাথে লব্ধির উৎপন্ন কোণ নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr"/>
+          <t>##PRESET:vector-addition[size:medium]##
+একটি স্টীমার স্রোতের অনুকূলে যেতে $4	ext{ ঘণ্টা}$ সময় নেয় এবং প্রতিকূলে ফিরে আসতে $6	ext{ ঘণ্টা}$ সময় নেয়। স্টীমারের ইঞ্জিন বন্ধ থাকলে কেবল স্রোতের টানে একই দূরত্ব অতিক্রম করতে কত ঘণ্টা সময় লাগবে?</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>##PRESET:vector-addition[size:medium]##</t>
+        </is>
+      </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>$R = \sqrt{7^2 + 6^2 + 2(7)(6)\cos(134^\circ)} = 5.16\text{ N}$।
-$\tan\theta = \frac{6\sin 134^\circ}{7 + 6\cos 134^\circ} \implies \theta = 56.73^\circ$।</t>
+          <t>$d = (v+u)4 \implies v+u = d/4$। $d = (v-u)6 \implies v-u = d/6$। বিয়োগ করে: $2u = \frac{d}{4} - \frac{d}{6} = \frac{d}{12} \implies u = \frac{d}{24}$। সুতরাং কেবল স্রোতে দূরত্ব $d$ যেতে সময় $T = \frac{d}{u} = 24\text{ h}$।</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>$R = 5.16\text{ N}, \theta = 56.73^\circ$</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
+          <t>সময় $T = 24\text{ ঘণ্টা}$</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -5661,21 +5347,21 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>ভেক্টর বিভাজন ও উপাংশ বিশ্লেষণ 33</t>
+          <t>নদী ও নৌকার গতি (River-Boat Relative Kinematics)</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
           <t>##PRESET:vector-addition[size:medium]##
-একটি বিন্দুতে $8\text{ N}$ এবং $7\text{ N}$ মানের দুটি বল পরস্পর $141^\circ$ কোণে ক্রিয়ারত। বলদ্বয়ের লব্ধির মান এবং ক্ষুদ্রতর বলটির সাথে লব্ধির উৎপন্ন কোণ নির্ণয় কর।</t>
+একটি নদী $600	ext{ m}$ চওড়া। একটি নৌকা $v = 5	ext{ m/s}$ বেগে চলে। স্রোতের বেগ $u = 3	ext{ m/s}$। নৌকাটি সর্বনিম্ন দূরত্বের পথে গেলে যে সময় লাগে এবং সর্বনিম্ন সময়ের পথে গেলে যে সময় লাগে তাদের পার্থক্য নির্ণয় কর।</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5685,19 +5371,14 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>$R = \sqrt{8^2 + 7^2 + 2(8)(7)\cos(141^\circ)} = 5.1\text{ N}$।
-$\tan\theta = \frac{7\sin 141^\circ}{8 + 7\cos 141^\circ} \implies \theta = 59.84^\circ$।</t>
+          <t>সর্বনিম্ন দূরত্বে: $w = \sqrt{5^2 - 3^2} = 4\text{ m/s}$। সময় $t_1 = \frac{600}{4} = 150\text{ s}$। সর্বনিম্ন সময়ে: $t_2 = \frac{600}{5} = 120\text{ s}$। পার্থক্য $\Delta t = 150 - 120 = 30\text{ s}$।</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>$R = 5.1\text{ N}, \theta = 59.84^\circ$</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr"/>
-      <c r="N84" t="inlineStr"/>
+          <t>সময়ের পার্থক্য $\Delta t = 30\text{ সেকেন্ড}$</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -5717,38 +5398,38 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>ভেক্টর বিভাজন ও উপাংশ বিশ্লেষণ 34</t>
+          <t>নদী ও নৌকার গতি (River-Boat Relative Kinematics)</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F85" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>একটি বিন্দুতে $9\text{ N}$ এবং $8\text{ N}$ মানের দুটি বল পরস্পর $148^\circ$ কোণে ক্রিয়ারত। বলদ্বয়ের লব্ধির মান এবং ক্ষুদ্রতর বলটির সাথে লব্ধির উৎপন্ন কোণ নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr"/>
+          <t>##PRESET:vector-addition[size:medium]##
+একজন সাঁতারুর সাঁতারের বেগ নদীর স্রোতের বেগের দ্বিগুণ ($v = 2u$)। সাঁতারু ন্যূনতম দূরত্বে নদী পার হতে চাইলে স্রোতের দিকের সাথে কত কোণে সাঁতার কাটবে?</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>##PRESET:vector-addition[size:medium]##</t>
+        </is>
+      </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>$R = \sqrt{9^2 + 8^2 + 2(9)(8)\cos(148^\circ)} = 4.78\text{ N}$।
-$\tan\theta = \frac{8\sin 148^\circ}{9 + 8\cos 148^\circ} \implies \theta = 62.41^\circ$।</t>
+          <t>ন্যূনতম দূরত্বে সোজা পৌঁছানোর শর্ত: $\cos\alpha = -\frac{u}{v} = -\frac{u}{2u} = -\frac{1}{2} \implies \alpha = 120^\circ$।</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>$R = 4.78\text{ N}, \theta = 62.41^\circ$</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr"/>
-      <c r="N85" t="inlineStr"/>
+          <t>$\alpha = 120^\circ$</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -5768,38 +5449,38 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>ভেক্টর বিভাজন ও উপাংশ বিশ্লেষণ 35</t>
+          <t>নদী ও নৌকার গতি (River-Boat Relative Kinematics)</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>একটি বিন্দুতে $3\text{ N}$ এবং $4\text{ N}$ মানের দুটি বল পরস্পর $35^\circ$ কোণে ক্রিয়ারত। বলদ্বয়ের লব্ধির মান এবং ক্ষুদ্রতর বলটির সাথে লব্ধির উৎপন্ন কোণ নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr"/>
+          <t>##PRESET:vector-addition[size:medium]##
+নদীতে স্থির পানিতে নৌকার বেগ $10	ext{ km/h}$ এবং স্রোতের বেগ $5	ext{ km/h}$। নৌকাটিকে নদীর পাড়ের সাথে কত কোণে চালালে এটি নদীর বিপরীত পাড়ে যাত্রা বিন্দুর ঠিক বিপরীতে গিয়ে পৌঁছাবে?</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>##PRESET:vector-addition[size:medium]##</t>
+        </is>
+      </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>$R = \sqrt{3^2 + 4^2 + 2(3)(4)\cos(35^\circ)} = 6.68\text{ N}$।
-$\tan\theta = \frac{4\sin 35^\circ}{3 + 4\cos 35^\circ} \implies \theta = 20.08^\circ$।</t>
+          <t>স্রোতের সাথে কোণ $\cos\alpha = -\frac{u}{v} = -\frac{5}{10} = -0.5 \implies \alpha = 120^\circ$। অতএব নদীর তীরের (পাড়ের) সাথে কোণ $= 180^\circ - 120^\circ = 60^\circ$ (অথবা উলম্বের সাথে $30^\circ$)।</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>$R = 6.68\text{ N}, \theta = 20.08^\circ$</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr"/>
-      <c r="N86" t="inlineStr"/>
+          <t>পাড়ের সাথে কোণ $\theta = 30^\circ$ (স্রোতের সাথে $120^\circ$)</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -5819,43 +5500,38 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>ভেক্টর বিভাজন ও উপাংশ বিশ্লেষণ 36</t>
+          <t>বৃষ্টি ও বাতাসের আপেক্ষিক বেগ, ডাইভারজেন্স ও কার্ল</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F87" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>##PRESET:vector-addition[size:medium]##
-একটি বিন্দুতে $4\text{ N}$ এবং $5\text{ N}$ মানের দুটি বল পরস্পর $42^\circ$ কোণে ক্রিয়ারত। বলদ্বয়ের লব্ধির মান এবং ক্ষুদ্রতর বলটির সাথে লব্ধির উৎপন্ন কোণ নির্ণয় কর।</t>
+          <t>##GEO:right-triangle[a=6,b=8,c=10,angle=53.1][size:small]##
+খাড়া নিচের দিকে $6	ext{ m/s}$ বেগে বৃষ্টি পড়ছে। একজন পথচারী $8	ext{ m/s}$ বেগে অনুভূমিক রাস্তায় সাইকেল চালিয়ে যাচ্ছেন। বৃষ্টি হতে বাঁচতে তাকে উল্লম্বের সাথে কত কোণে ছাতা ধরতে হবে?</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>##PRESET:vector-addition[size:medium]##</t>
+          <t>##GEO:right-triangle[a=6,b=8,c=10,angle=53.1][size:small]##</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>$R = \sqrt{4^2 + 5^2 + 2(4)(5)\cos(42^\circ)} = 8.41\text{ N}$।
-$\tan\theta = \frac{5\sin 42^\circ}{4 + 5\cos 42^\circ} \implies \theta = 23.44^\circ$।</t>
+          <t>বৃষ্টির বেগ $\vec{v}_r = -6\hat{j}$, পথচারীর বেগ $\vec{v}_m = 8\hat{i}$। পথচারীর সাপেক্ষে বৃষ্টির আপেক্ষিক বেগ $\vec{v}_{r/m} = \vec{v}_r - \vec{v}_m = -8\hat{i} - 6\hat{j}$। উল্লম্বের সাথে উৎপন্ন কোণ $\tan\theta = \frac{|v_m|}{|v_r|} = \frac{8}{6} = \frac{4}{3} \implies \theta = \tan^{-1}(1.333) \approx 53.13^\circ$ সামনের দিকে।</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>$R = 8.41\text{ N}, \theta = 23.44^\circ$</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
+          <t>$\theta = \tan^{-1}\left(\frac{4}{3}\right) \approx 53.13^\circ$</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -5875,38 +5551,38 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>ভেক্টর বিভাজন ও উপাংশ বিশ্লেষণ 37</t>
+          <t>বৃষ্টি ও বাতাসের আপেক্ষিক বেগ, ডাইভারজেন্স ও কার্ল</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>একটি বিন্দুতে $5\text{ N}$ এবং $6\text{ N}$ মানের দুটি বল পরস্পর $49^\circ$ কোণে ক্রিয়ারত। বলদ্বয়ের লব্ধির মান এবং ক্ষুদ্রতর বলটির সাথে লব্ধির উৎপন্ন কোণ নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr"/>
+          <t>##PRESET:vector-addition[size:medium]##
+খাড়া নিচে $10	ext{ m/s}$ দ্রুতিতে বৃষ্টি পড়ছে এবং অনুভূমিকভাবে পূর্ব হতে পশ্চিমে $5	ext{ m/s}$ বেগে বাতাস বইছে। একজন লোক কত বেগে পশ্চিম হতে পূর্বে হাঁটলে তার গায়ে বৃষ্টি খাড়া নিচে পড়বে?</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>##PRESET:vector-addition[size:medium]##</t>
+        </is>
+      </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>$R = \sqrt{5^2 + 6^2 + 2(5)(6)\cos(49^\circ)} = 10.02\text{ N}$।
-$\tan\theta = \frac{6\sin 49^\circ}{5 + 6\cos 49^\circ} \implies \theta = 26.87^\circ$।</t>
+          <t>বাতাসের সাথে বৃষ্টির অনুভূমিক বেগ $v_{rx} = -5\hat{i}$ (পূর্ব হতে পশ্চিম)। লোকটির বেগ $\vec{v}_m = v_m \hat{i}$ (পশ্চিম হতে পূর্ব)। আপেক্ষিক অনুভূমিক বেগ $= v_{rx} - v_m = -5 - v_m = 0$ হতে হবে উল্লম্বভাবে পড়ার জন্য $\implies$ লোকটিকে বাতাসের অভিমুখে $5\text{ m/s}$ বেগে যেতে হবে।</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>$R = 10.02\text{ N}, \theta = 26.87^\circ$</t>
-        </is>
-      </c>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr"/>
-      <c r="N88" t="inlineStr"/>
+          <t>$v_m = 5\text{ m/s}$ পশ্চিম হতে পূর্ব দিকে</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -5926,38 +5602,38 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>ভেক্টর বিভাজন ও উপাংশ বিশ্লেষণ 38</t>
+          <t>বৃষ্টি ও বাতাসের আপেক্ষিক বেগ, ডাইভারজেন্স ও কার্ল</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F89" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>একটি বিন্দুতে $6\text{ N}$ এবং $7\text{ N}$ মানের দুটি বল পরস্পর $56^\circ$ কোণে ক্রিয়ারত। বলদ্বয়ের লব্ধির মান এবং ক্ষুদ্রতর বলটির সাথে লব্ধির উৎপন্ন কোণ নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr"/>
+          <t>##GEO:triangle[a=4,b=6,c=7][size:small]##
+একজন সাইকেল আরোহী $4	ext{ m/s}$ বেগে চলার সময় উল্লম্বের সাথে $30^\circ$ কোণে ছাতা ধরে বৃষ্টি থেকে রক্ষা পান। গতিবেগ বৃদ্ধি করে $8	ext{ m/s}$ করলে তাকে উল্লম্বের সাথে $45^\circ$ কোণে ছাতা ধরতে হয়। বৃষ্টির প্রকৃত বেগ এবং পতনের দিক নির্ণয় কর।</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>##GEO:triangle[a=4,b=6,c=7][size:small]##</t>
+        </is>
+      </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>$R = \sqrt{6^2 + 7^2 + 2(6)(7)\cos(56^\circ)} = 11.49\text{ N}$।
-$\tan\theta = \frac{7\sin 56^\circ}{6 + 7\cos 56^\circ} \implies \theta = 30.34^\circ$।</t>
+          <t>ধরি বৃষ্টির অনুভূমিক বেগ $v_x$ এবং উল্লম্ব বেগ $v_y$। প্রথম ক্ষেত্রে: $\tan 30^\circ = \frac{4 - v_x}{v_y} = \frac{1}{\sqrt{3}}$। দ্বিতীয় ক্ষেত্রে: $\tan 45^\circ = \frac{8 - v_x}{v_y} = 1 \implies 8 - v_x = v_y$। সমীকরণ সমাধান করে $v_x \approx 1.93\text{ m/s}, v_y \approx 6.07\text{ m/s}$। $v_r = \sqrt{v_x^2 + v_y^2} \approx 6.37\text{ m/s}$।</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>$R = 11.49\text{ N}, \theta = 30.34^\circ$</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr"/>
-      <c r="N89" t="inlineStr"/>
+          <t>বৃষ্টির বেগ $v_r = 7.18\text{ m/s}$, খাড়া নিচের সাথে কোণ $15.5^\circ$</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -5977,43 +5653,39 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>ভেক্টর বিভাজন ও উপাংশ বিশ্লেষণ 39</t>
+          <t>বৃষ্টি ও বাতাসের আপেক্ষিক বেগ, ডাইভারজেন্স ও কার্ল</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F90" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>##PRESET:vector-addition[size:medium]##
-একটি বিন্দুতে $7\text{ N}$ এবং $8\text{ N}$ মানের দুটি বল পরস্পর $63^\circ$ কোণে ক্রিয়ারত। বলদ্বয়ের লব্ধির মান এবং ক্ষুদ্রতর বলটির সাথে লব্ধির উৎপন্ন কোণ নির্ণয় কর।</t>
+          <t>##PRESET:vector-cross[size:medium]##
+একটি ভেক্টর ক্ষেত্র $ec{F} = (x^2 y)\hat{i} - (2 x z)\hat{j} + (2 y z)\hat{k}$। বিন্দু $(1, -1, 2)$ এ ভেক্টর ক্ষেত্রের ডাইভারজেন্স $
+abla \cdot ec{F}$ নির্ণয় কর। ক্ষেত্রটি কি সলিনয়ডাল (Solenoidal)?</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>##PRESET:vector-addition[size:medium]##</t>
+          <t>##PRESET:vector-cross[size:medium]##</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>$R = \sqrt{7^2 + 8^2 + 2(7)(8)\cos(63^\circ)} = 12.8\text{ N}$।
-$\tan\theta = \frac{8\sin 63^\circ}{7 + 8\cos 63^\circ} \implies \theta = 33.84^\circ$।</t>
+          <t>$\nabla \cdot \vec{F} = \frac{\partial}{\partial x}(x^2 y) + \frac{\partial}{\partial y}(-2 x z) + \frac{\partial}{\partial z}(2 y z) = 2xy + 0 + 2y = 2y(x+1)$। $(1, -1, 2)$ বিন্দুতে ডাইভারজেন্স $= 2(-1)(1+1) = -4$। যেহেতু ডাইভারজেন্স শূন্য নয়, তাই ক্ষেত্রটি সলিনয়ডাল নয়।</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>$R = 12.8\text{ N}, \theta = 33.84^\circ$</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr"/>
-      <c r="N90" t="inlineStr"/>
+          <t>$\nabla \cdot \vec{F} = -4$, ক্ষেত্রটি সলিনয়ডাল নয়</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -6033,38 +5705,38 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>ভেক্টর বিভাজন ও উপাংশ বিশ্লেষণ 40</t>
+          <t>বৃষ্টি ও বাতাসের আপেক্ষিক বেগ, ডাইভারজেন্স ও কার্ল</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F91" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>একটি বিন্দুতে $8\text{ N}$ এবং $4\text{ N}$ মানের দুটি বল পরস্পর $70^\circ$ কোণে ক্রিয়ারত। বলদ্বয়ের লব্ধির মান এবং ক্ষুদ্রতর বলটির সাথে লব্ধির উৎপন্ন কোণ নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr"/>
+          <t>##PRESET:vector-addition[size:medium]##
+ধ্রুবক $a$-এর মান কত হলে ভেক্টর ক্ষেত্র $ec{V} = (x + 3y)\hat{i} + (y - 2z)\hat{j} + (x + a z)\hat{k}$ সলিনয়ডাল (Solenoidal) হবে?</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>##PRESET:vector-addition[size:medium]##</t>
+        </is>
+      </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>$R = \sqrt{8^2 + 4^2 + 2(8)(4)\cos(70^\circ)} = 10.09\text{ N}$।
-$\tan\theta = \frac{4\sin 70^\circ}{8 + 4\cos 70^\circ} \implies \theta = 21.86^\circ$।</t>
+          <t>সলিনয়ডাল হওয়ার শর্ত $\nabla \cdot \vec{V} = 0$। $\frac{\partial}{\partial x}(x+3y) + \frac{\partial}{\partial y}(y-2z) + \frac{\partial}{\partial z}(x+az) = 0 \implies 1 + 1 + a = 0 \implies 2 + a = 0 \implies a = -2$।</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>$R = 10.09\text{ N}, \theta = 21.86^\circ$</t>
-        </is>
-      </c>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr"/>
-      <c r="N91" t="inlineStr"/>
+          <t>$a = -2$</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -6084,38 +5756,39 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>ভেক্টর বিভাজন ও উপাংশ বিশ্লেষণ 41</t>
+          <t>বৃষ্টি ও বাতাসের আপেক্ষিক বেগ, ডাইভারজেন্স ও কার্ল</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>একটি বিন্দুতে $9\text{ N}$ এবং $5\text{ N}$ মানের দুটি বল পরস্পর $77^\circ$ কোণে ক্রিয়ারত। বলদ্বয়ের লব্ধির মান এবং ক্ষুদ্রতর বলটির সাথে লব্ধির উৎপন্ন কোণ নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr"/>
+          <t>##PRESET:vector-cross[size:medium]##
+একটি বল ক্ষেত্র $ec{F} = (2xy + z^3)\hat{i} + x^2\hat{j} + 3xz^2\hat{k}$। প্রমাণ কর যে বল ক্ষেত্রটি একটি সংরক্ষণশীল বল ক্ষেত্র এবং এর কার্ল $
+abla 	imes ec{F} = 0$ (অঘূর্ণনশীল)।</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>##PRESET:vector-cross[size:medium]##</t>
+        </is>
+      </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>$R = \sqrt{9^2 + 5^2 + 2(9)(5)\cos(77^\circ)} = 11.24\text{ N}$।
-$\tan\theta = \frac{5\sin 77^\circ}{9 + 5\cos 77^\circ} \implies \theta = 25.7^\circ$।</t>
+          <t>$\nabla \times \vec{F} = \begin{vmatrix} \hat{i} &amp; \hat{j} &amp; \hat{k} \\ \partial_x &amp; \partial_y &amp; \partial_z \\ 2xy+z^3 &amp; x^2 &amp; 3xz^2 \end{vmatrix} = \hat{i}(0 - 0) - \hat{j}(3z^2 - 3z^2) + \hat{k}(2x - 2x) = 0\hat{i} + 0\hat{j} + 0\hat{k} = \vec{0}$। কার্ল শূন্য হওয়ায় ক্ষেত্রটি অঘূর্ণনশীল এবং সংরক্ষণশীল।</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>$R = 11.24\text{ N}, \theta = 25.7^\circ$</t>
-        </is>
-      </c>
-      <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
-      <c r="M92" t="inlineStr"/>
-      <c r="N92" t="inlineStr"/>
+          <t>$\nabla \times \vec{F} = \vec{0}$, ক্ষেত্রটি সংরক্ষণশীল</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -6135,43 +5808,38 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>ভেক্টর বিভাজন ও উপাংশ বিশ্লেষণ 42</t>
+          <t>বৃষ্টি ও বাতাসের আপেক্ষিক বেগ, ডাইভারজেন্স ও কার্ল</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F93" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>##PRESET:vector-addition[size:medium]##
-একটি বিন্দুতে $3\text{ N}$ এবং $6\text{ N}$ মানের দুটি বল পরস্পর $84^\circ$ কোণে ক্রিয়ারত। বলদ্বয়ের লব্ধির মান এবং ক্ষুদ্রতর বলটির সাথে লব্ধির উৎপন্ন কোণ নির্ণয় কর।</t>
+          <t>##PRESET:vector-cross[size:medium]##
+ধ্রুবক $k$-এর মান কত হলে ভেক্টর ক্ষেত্র $ec{A} = (x + 2y + 4z)\hat{i} + (2x - 3y - z)\hat{j} + (kx - y + 2z)\hat{k}$ অঘূর্ণনশীল (Irrotational) হবে?</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>##PRESET:vector-addition[size:medium]##</t>
+          <t>##PRESET:vector-cross[size:medium]##</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>$R = \sqrt{3^2 + 6^2 + 2(3)(6)\cos(84^\circ)} = 6.98\text{ N}$।
-$\tan\theta = \frac{6\sin 84^\circ}{3 + 6\cos 84^\circ} \implies \theta = 58.71^\circ$।</t>
+          <t>অঘূর্ণনশীল হওয়ার জন্য $\nabla \times \vec{A} = \vec{0}$ হতে হবে। এর $j$-উপাংশ: $\frac{\partial}{\partial z}(x+2y+4z) - \frac{\partial}{\partial x}(kx-y+2z) = 0 \implies 4 - k = 0 \implies k = 4$।</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>$R = 6.98\text{ N}, \theta = 58.71^\circ$</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
-      <c r="M93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
+          <t>$k = 4$</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -6191,38 +5859,40 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>ভেক্টর বিভাজন ও উপাংশ বিশ্লেষণ 43</t>
+          <t>বৃষ্টি ও বাতাসের আপেক্ষিক বেগ, ডাইভারজেন্স ও কার্ল</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>একটি বিন্দুতে $4\text{ N}$ এবং $7\text{ N}$ মানের দুটি বল পরস্পর $91^\circ$ কোণে ক্রিয়ারত। বলদ্বয়ের লব্ধির মান এবং ক্ষুদ্রতর বলটির সাথে লব্ধির উৎপন্ন কোণ নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr"/>
+          <t>##PRESET:vector-cross[size:medium]##
+অবস্থান ভেক্টর $ec{r} = x\hat{i} + y\hat{j} + z\hat{k}$ এবং $r = |ec{r}|$ হলে প্রমাণ কর যে $
+abla \cdot ec{r} = 3$ এবং $
+abla 	imes ec{r} = ec{0}$।</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>##PRESET:vector-cross[size:medium]##</t>
+        </is>
+      </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>$R = \sqrt{4^2 + 7^2 + 2(4)(7)\cos(91^\circ)} = 8.0\text{ N}$।
-$\tan\theta = \frac{7\sin 91^\circ}{4 + 7\cos 91^\circ} \implies \theta = 61.01^\circ$।</t>
+          <t>$\nabla \cdot \vec{r} = \frac{\partial x}{\partial x} + \frac{\partial y}{\partial y} + \frac{\partial z}{\partial z} = 1 + 1 + 1 = 3$। $\nabla \times \vec{r} = \begin{vmatrix} \hat{i} &amp; \hat{j} &amp; \hat{k} \\ \partial_x &amp; \partial_y &amp; \partial_z \\ x &amp; y &amp; z \end{vmatrix} = \hat{i}(0) - \hat{j}(0) + \hat{k}(0) = \vec{0}$।</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>$R = 8.0\text{ N}, \theta = 61.01^\circ$</t>
-        </is>
-      </c>
-      <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr"/>
-      <c r="N94" t="inlineStr"/>
+          <t>$\nabla \cdot \vec{r} = 3, \nabla \times \vec{r} = \vec{0}$</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -6242,38 +5912,38 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>ভেক্টর বিভাজন ও উপাংশ বিশ্লেষণ 44</t>
+          <t>বৃষ্টি ও বাতাসের আপেক্ষিক বেগ, ডাইভারজেন্স ও কার্ল</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F95" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>একটি বিন্দুতে $5\text{ N}$ এবং $8\text{ N}$ মানের দুটি বল পরস্পর $98^\circ$ কোণে ক্রিয়ারত। বলদ্বয়ের লব্ধির মান এবং ক্ষুদ্রতর বলটির সাথে লব্ধির উৎপন্ন কোণ নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr"/>
+          <t>##PRESET:vector-cross[size:medium]##
+একটি ঘূর্ণায়মান বস্তুর কৌণিক বেগ $ec{\omega} = 2\hat{i} - 3\hat{j} + 4\hat{k}	ext{ rad/s}$ এবং ঘূর্ণন অক্ষ সাপেক্ষে অবস্থান ভেক্টর $ec{r} = 3\hat{i} + 2\hat{j} - \hat{k}	ext{ m}$ হলে রৈখিক বেগ $ec{v} = ec{\omega} 	imes ec{r}$ এর ভেক্টর মান নির্ণয় কর।</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>##PRESET:vector-cross[size:medium]##</t>
+        </is>
+      </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>$R = \sqrt{5^2 + 8^2 + 2(5)(8)\cos(98^\circ)} = 8.82\text{ N}$।
-$\tan\theta = \frac{8\sin 98^\circ}{5 + 8\cos 98^\circ} \implies \theta = 63.87^\circ$।</t>
+          <t>$\vec{v} = \vec{\omega} \times \vec{r} = \begin{vmatrix} \hat{i} &amp; \hat{j} &amp; \hat{k} \\ 2 &amp; -3 &amp; 4 \\ 3 &amp; 2 &amp; -1 \end{vmatrix} = \hat{i}(3 - 8) - \hat{j}(-2 - 12) + \hat{k}(4 - (-9)) = -5\hat{i} + 14\hat{j} + 13\hat{k}\text{ m/s}$। মান $|\vec{v}| = \sqrt{25 + 196 + 169} = \sqrt{390} \approx 19.75\text{ m/s}$।</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>$R = 8.82\text{ N}, \theta = 63.87^\circ$</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
+          <t>$\vec{v} = -5\hat{i} + 14\hat{j} + 13\hat{k}\text{ m/s}, |\vec{v}| = 19.75\text{ m/s}$</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -6293,21 +5963,22 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>ভেক্টর বিভাজন ও উপাংশ বিশ্লেষণ 45</t>
+          <t>বৃষ্টি ও বাতাসের আপেক্ষিক বেগ, ডাইভারজেন্স ও কার্ল</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F96" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
           <t>##PRESET:vector-addition[size:medium]##
-একটি বিন্দুতে $6\text{ N}$ এবং $4\text{ N}$ মানের দুটি বল পরস্পর $105^\circ$ কোণে ক্রিয়ারত। বলদ্বয়ের লব্ধির মান এবং ক্ষুদ্রতর বলটির সাথে লব্ধির উৎপন্ন কোণ নির্ণয় কর।</t>
+একটি স্কেলার ক্ষেত্র $\phi(x, y, z) = 2x^2 y - 3y^2 z + x z^3$ হলে বিন্দু $(1, 1, 1)$ এ এর নতিমাত্রা (Gradient) $
+abla\phi$ নির্ণয় কর।</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -6317,19 +5988,14 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>$R = \sqrt{6^2 + 4^2 + 2(6)(4)\cos(105^\circ)} = 6.29\text{ N}$।
-$\tan\theta = \frac{4\sin 105^\circ}{6 + 4\cos 105^\circ} \implies \theta = 37.89^\circ$।</t>
+          <t>$\frac{\partial\phi}{\partial x} = 4xy + z^3 \implies 4(1)(1) + 1^3 = 5$। $\frac{\partial\phi}{\partial y} = 2x^2 - 6yz \implies 2(1) - 6(1)(1) = -4$। $\frac{\partial\phi}{\partial z} = -3y^2 + 3xz^2 \implies -3(1) + 3(1)(1) = 0$। অতএব $\nabla\phi = 5\hat{i} - 4\hat{j} + 0\hat{k}$।</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>$R = 6.29\text{ N}, \theta = 37.89^\circ$</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr"/>
-      <c r="N96" t="inlineStr"/>
+          <t>$\nabla\phi = 5\hat{i} - 4\hat{j} - 0\hat{k}$</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -6349,38 +6015,38 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>ভেক্টর বিভাজন ও উপাংশ বিশ্লেষণ 46</t>
+          <t>বৃষ্টি ও বাতাসের আপেক্ষিক বেগ, ডাইভারজেন্স ও কার্ল</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F97" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>একটি বিন্দুতে $7\text{ N}$ এবং $5\text{ N}$ মানের দুটি বল পরস্পর $112^\circ$ কোণে ক্রিয়ারত। বলদ্বয়ের লব্ধির মান এবং ক্ষুদ্রতর বলটির সাথে লব্ধির উৎপন্ন কোণ নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr"/>
+          <t>##GEO:right-triangle[a=4,b=3,c=5,angle=36.9][size:small]##
+খাড়া নিচের দিকে $4	ext{ m/s}$ বেগে বৃষ্টি পড়ছে এবং অনুভূমিকভাবে $3	ext{ m/s}$ বেগে বাতাস বইছে। একজন লোক স্থির দাঁড়িয়ে থাকলে তার গায়ে বৃষ্টি কত বেগে এবং কত কোণে পড়বে?</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>##GEO:right-triangle[a=4,b=3,c=5,angle=36.9][size:small]##</t>
+        </is>
+      </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>$R = \sqrt{7^2 + 5^2 + 2(7)(5)\cos(112^\circ)} = 6.91\text{ N}$।
-$\tan\theta = \frac{5\sin 112^\circ}{7 + 5\cos 112^\circ} \implies \theta = 42.12^\circ$।</t>
+          <t>বৃষ্টির বেগ $\vec{v}_R = 3\hat{i} - 4\hat{j}$। মান $v = \sqrt{3^2 + (-4)^2} = 5\text{ m/s}$। উল্লম্বের সাথে কোণ $\tan\theta = \frac{v_x}{v_y} = \frac{3}{4} = 0.75 \implies \theta = 36.87^\circ$।</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>$R = 6.91\text{ N}, \theta = 42.12^\circ$</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr"/>
-      <c r="N97" t="inlineStr"/>
+          <t>বৃষ্টির লব্ধি বেগ $5\text{ m/s}$, উল্লম্বের সাথে কোণ $36.87^\circ$</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -6400,38 +6066,38 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>ভেক্টর বিভাজন ও উপাংশ বিশ্লেষণ 47</t>
+          <t>বৃষ্টি ও বাতাসের আপেক্ষিক বেগ, ডাইভারজেন্স ও কার্ল</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F98" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>একটি বিন্দুতে $8\text{ N}$ এবং $6\text{ N}$ মানের দুটি বল পরস্পর $119^\circ$ কোণে ক্রিয়ারত। বলদ্বয়ের লব্ধির মান এবং ক্ষুদ্রতর বলটির সাথে লব্ধির উৎপন্ন কোণ নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr"/>
+          <t>##PRESET:vector-cross[size:medium]##
+একটি ভেক্টর $ec{A} = 3\hat{i} + 4\hat{j}$। ভেক্টরটির সমতলে অবস্থিত এবং $ec{A}$-এর ওপর লম্ব এমন একটি একক ভেক্টর নির্ণয় কর।</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>##PRESET:vector-cross[size:medium]##</t>
+        </is>
+      </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>$R = \sqrt{8^2 + 6^2 + 2(8)(6)\cos(119^\circ)} = 7.31\text{ N}$।
-$\tan\theta = \frac{6\sin 119^\circ}{8 + 6\cos 119^\circ} \implies \theta = 45.87^\circ$।</t>
+          <t>ধরি লম্ব ভেক্টর $\vec{B} = B_x \hat{i} + B_y \hat{j}$। $\vec{A} \cdot \vec{B} = 0 \implies 3 B_x + 4 B_y = 0 \implies B_y = -\frac{3}{4} B_x$। একক ভেক্টর $\hat{n} = \frac{B_x \hat{i} - \frac{3}{4}B_x \hat{j}}{\sqrt{B_x^2 + \frac{9}{16}B_x^2}} = \pm \frac{4\hat{i} - 3\hat{j}}{5}$।</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>$R = 7.31\text{ N}, \theta = 45.87^\circ$</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr"/>
-      <c r="N98" t="inlineStr"/>
+          <t>$\hat{n} = \pm \frac{4\hat{i} - 3\hat{j}}{5}$</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -6451,21 +6117,22 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>ভেক্টর বিভাজন ও উপাংশ বিশ্লেষণ 48</t>
+          <t>বৃষ্টি ও বাতাসের আপেক্ষিক বেগ, ডাইভারজেন্স ও কার্ল</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F99" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
           <t>##PRESET:vector-addition[size:medium]##
-একটি বিন্দুতে $9\text{ N}$ এবং $7\text{ N}$ মানের দুটি বল পরস্পর $126^\circ$ কোণে ক্রিয়ারত। বলদ্বয়ের লব্ধির মান এবং ক্ষুদ্রতর বলটির সাথে লব্ধির উৎপন্ন কোণ নির্ণয় কর।</t>
+ভেক্টর ক্ষেত্র $ec{v} = (y^2)\hat{i} + (2xy + z^2)\hat{j} + (2yz)\hat{k}$। দেখাও যে ক্ষেত্রটি সংরক্ষণশীল এবং এর সাথে সংশ্লিষ্ট স্কেলার বিভব $\phi(x, y, z)$ নির্ণয় কর যেখানে $ec{v} = 
+abla\phi$।</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -6475,19 +6142,14 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>$R = \sqrt{9^2 + 7^2 + 2(9)(7)\cos(126^\circ)} = 7.48\text{ N}$।
-$\tan\theta = \frac{7\sin 126^\circ}{9 + 7\cos 126^\circ} \implies \theta = 49.22^\circ$।</t>
+          <t>$\frac{\partial\phi}{\partial x} = y^2 \implies \phi = x y^2 + f(y, z)$। $\frac{\partial\phi}{\partial y} = 2xy + \frac{\partial f}{\partial y} = 2xy + z^2 \implies f = y z^2 + g(z)$। $\frac{\partial\phi}{\partial z} = 2yz + g'(z) = 2yz \implies g'(z) = 0 \implies g(z) = C$। অতএব বিভব $\phi(x, y, z) = x y^2 + y z^2 + C$।</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>$R = 7.48\text{ N}, \theta = 49.22^\circ$</t>
-        </is>
-      </c>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr"/>
-      <c r="N99" t="inlineStr"/>
+          <t>$\phi(x, y, z) = x y^2 + y z^2 + C$</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -6507,38 +6169,38 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>ভেক্টর বিভাজন ও উপাংশ বিশ্লেষণ 49</t>
+          <t>বৃষ্টি ও বাতাসের আপেক্ষিক বেগ, ডাইভারজেন্স ও কার্ল</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F100" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>একটি বিন্দুতে $3\text{ N}$ এবং $8\text{ N}$ মানের দুটি বল পরস্পর $133^\circ$ কোণে ক্রিয়ারত। বলদ্বয়ের লব্ধির মান এবং ক্ষুদ্রতর বলটির সাথে লব্ধির উৎপন্ন কোণ নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr"/>
+          <t>##GEO:cube[s=3][size:small]##
+একটি সমান্তরাল পাইপড (Parallelepiped) এর তিনটি সহ-প্রারম্ভিক ধার যথাক্রমে $ec{a} = 2\hat{i} - 3\hat{j} + 4\hat{k}$, $ec{b} = \hat{i} + 2\hat{j} - \hat{k}$ এবং $ec{c} = 3\hat{i} - \hat{j} + 2\hat{k}$ দ্বারা সূচিত হলে এর আয়তন কত?</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>##GEO:cube[s=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>$R = \sqrt{3^2 + 8^2 + 2(3)(8)\cos(133^\circ)} = 6.35\text{ N}$।
-$\tan\theta = \frac{8\sin 133^\circ}{3 + 8\cos 133^\circ} \implies \theta = 112.77^\circ$।</t>
+          <t>আয়তন $V = \vec{a} \cdot (\vec{b} \times \vec{c}) = \begin{vmatrix} 2 &amp; -3 &amp; 4 \\ 1 &amp; 2 &amp; -1 \\ 3 &amp; -1 &amp; 2 \end{vmatrix} = 2(4 - 1) - (-3)(2 - (-3)) + 4(-1 - 6) = 2(3) + 3(5) + 4(-7) = 6 + 15 - 28 = -7$। সুতরাং আয়তন $= |-7| = 7\text{ ঘন একক}$।</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>$R = 6.35\text{ N}, \theta = 112.77^\circ$</t>
-        </is>
-      </c>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr"/>
-      <c r="N100" t="inlineStr"/>
+          <t>আয়তন $V = -7\text{ ঘন একক (মান } 7\text{ ঘন একক)}$</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -6558,38 +6220,38 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>ভেক্টর বিভাজন ও উপাংশ বিশ্লেষণ 50</t>
+          <t>বৃষ্টি ও বাতাসের আপেক্ষিক বেগ, ডাইভারজেন্স ও কার্ল</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F101" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>একটি বিন্দুতে $4\text{ N}$ এবং $4\text{ N}$ মানের দুটি বল পরস্পর $140^\circ$ কোণে ক্রিয়ারত। বলদ্বয়ের লব্ধির মান এবং ক্ষুদ্রতর বলটির সাথে লব্ধির উৎপন্ন কোণ নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr"/>
+          <t>##GEO:right-triangle[a=3,b=5.2,angle=30][size:small]##
+একজন লোক $30^\circ$ ঢালু একটি পাহাড় বরাবর $6	ext{ km/h}$ বেগে উপরে উঠছে। খাড়া নিচের দিকে $8	ext{ km/h}$ বেগে বৃষ্টি পড়লে আরোহীকে কত কোণে ছাতা ধরতে হবে?</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>##GEO:right-triangle[a=3,b=5.2,angle=30][size:small]##</t>
+        </is>
+      </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>$R = \sqrt{4^2 + 4^2 + 2(4)(4)\cos(140^\circ)} = 2.74\text{ N}$।
-$\tan\theta = \frac{4\sin 140^\circ}{4 + 4\cos 140^\circ} \implies \theta = 70.0^\circ$।</t>
+          <t>বৃষ্টির বেগ $\vec{v}_r = -8\hat{j}$। আরোহীর বেগ $\vec{v}_m = 6\cos 30^\circ \hat{i} + 6\sin 30^\circ \hat{j} = 3\sqrt{3}\hat{i} + 3\hat{j}$। আপেক্ষিক বেগ $\vec{v}_{r/m} = \vec{v}_r - \vec{v}_m = -3\sqrt{3}\hat{i} - 11\hat{j}$। উল্লম্বের সাথে কোণ $\tan\theta = \frac{3\sqrt{3}}{11} = \frac{5.196}{11} \approx 0.472 \implies \theta \approx 25.3^\circ$। পাহাড়ের তলের সাপেক্ষে কোণ $= 30^\circ + 25.3^\circ \approx 55.3^\circ$।</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>$R = 2.74\text{ N}, \theta = 70.0^\circ$</t>
-        </is>
-      </c>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
-      <c r="M101" t="inlineStr"/>
-      <c r="N101" t="inlineStr"/>
+          <t>পাহাড়ের তলের সাথে কোণ $\approx 47.9^\circ$</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
